--- a/docs/data/教育后勤2025经营数据看版_组织标签映射表-勿动.xlsx
+++ b/docs/data/教育后勤2025经营数据看版_组织标签映射表-勿动.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="23040" windowHeight="9060"/>
+    <workbookView windowWidth="23040" windowHeight="9060" tabRatio="526"/>
   </bookViews>
   <sheets>
     <sheet name="组织标签映射表-勿动" sheetId="2" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1329" uniqueCount="203">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1285" uniqueCount="203">
   <si>
     <t>文本</t>
   </si>
@@ -62,15 +62,24 @@
     <t>整体查验</t>
   </si>
   <si>
+    <t>level1</t>
+  </si>
+  <si>
+    <t>level2</t>
+  </si>
+  <si>
+    <t>node</t>
+  </si>
+  <si>
     <t>后勤管理中心</t>
   </si>
   <si>
+    <t>其他</t>
+  </si>
+  <si>
     <t>海亮后勤车队</t>
   </si>
   <si>
-    <t>其他</t>
-  </si>
-  <si>
     <t>一致</t>
   </si>
   <si>
@@ -107,27 +116,21 @@
     <t>融爱星餐饮</t>
   </si>
   <si>
-    <t>教育园店</t>
-  </si>
-  <si>
     <t>融爱星餐饮-教育园店</t>
   </si>
   <si>
-    <t>社会店</t>
-  </si>
-  <si>
     <t>融爱星餐饮-杭州科研大厦店</t>
   </si>
   <si>
     <t>中心管理部门</t>
   </si>
   <si>
+    <t>管理部门</t>
+  </si>
+  <si>
     <t>后勤安全管理部</t>
   </si>
   <si>
-    <t>管理部门</t>
-  </si>
-  <si>
     <t>后勤餐饮运营部</t>
   </si>
   <si>
@@ -152,24 +155,21 @@
     <t>科研大厦食堂</t>
   </si>
   <si>
+    <t>中心物业业务</t>
+  </si>
+  <si>
     <t>湘湖后勤</t>
   </si>
   <si>
-    <t>中心物业业务</t>
-  </si>
-  <si>
-    <t>三大区域</t>
-  </si>
-  <si>
     <t>西南区域</t>
   </si>
   <si>
+    <t>区域配送业务</t>
+  </si>
+  <si>
     <t>存量</t>
   </si>
   <si>
-    <t>区域配送业务</t>
-  </si>
-  <si>
     <t>江陵配送</t>
   </si>
   <si>
@@ -308,10 +308,10 @@
     <t>西南新拓培训业务1</t>
   </si>
   <si>
+    <t>区域总经理室</t>
+  </si>
+  <si>
     <t>区域管理部门</t>
-  </si>
-  <si>
-    <t>区域总经理室</t>
   </si>
   <si>
     <t>西南区域总经理室</t>
@@ -812,12 +812,18 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="33">
+  <fills count="34">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -1136,7 +1142,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1160,16 +1166,16 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
@@ -1178,91 +1184,95 @@
     <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1584,13 +1594,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:K154"/>
+  <dimension ref="A1:K155"/>
   <sheetFormatPr defaultColWidth="10" defaultRowHeight="13.8"/>
   <cols>
-    <col min="1" max="3" width="19" customWidth="1"/>
-    <col min="4" max="4" width="22.3333333333333" customWidth="1"/>
-    <col min="5" max="5" width="19" customWidth="1"/>
-    <col min="6" max="6" width="21.8888888888889" customWidth="1"/>
+    <col min="1" max="2" width="19" customWidth="1"/>
+    <col min="3" max="3" width="17.2222222222222" customWidth="1"/>
+    <col min="4" max="4" width="15.1111111111111" style="1" customWidth="1"/>
+    <col min="5" max="5" width="19" style="1" customWidth="1"/>
+    <col min="6" max="6" width="27.7777777777778" customWidth="1"/>
     <col min="7" max="7" width="15.8888888888889" customWidth="1"/>
     <col min="8" max="8" width="16.4444444444444" customWidth="1"/>
     <col min="9" max="9" width="15.2222222222222" customWidth="1"/>
@@ -1599,125 +1610,101 @@
   </cols>
   <sheetData>
     <row r="1" ht="13" customHeight="1" spans="1:11">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="J1" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="K1" s="2" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="2" ht="25.5" customHeight="1" spans="1:11">
-      <c r="A2">
-        <v>1</v>
-      </c>
-      <c r="B2" t="s">
+    <row r="2" ht="13" customHeight="1" spans="1:11">
+      <c r="A2" s="2"/>
+      <c r="B2" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C2" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="D2" t="s">
-        <v>12</v>
-      </c>
-      <c r="E2" t="s">
+      <c r="D2" s="3"/>
+      <c r="E2" s="3"/>
+      <c r="F2" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="F2" t="s">
-        <v>12</v>
-      </c>
-      <c r="G2" t="s">
-        <v>12</v>
-      </c>
-      <c r="H2" t="s">
-        <v>12</v>
-      </c>
-      <c r="I2" t="s">
-        <v>12</v>
-      </c>
-      <c r="J2" t="s">
-        <v>12</v>
-      </c>
-      <c r="K2" t="s">
-        <v>14</v>
-      </c>
+      <c r="G2" s="2"/>
+      <c r="H2" s="2"/>
+      <c r="I2" s="2"/>
+      <c r="J2" s="2"/>
+      <c r="K2" s="2"/>
     </row>
     <row r="3" ht="25.5" customHeight="1" spans="1:11">
       <c r="A3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C3"/>
+      <c r="D3" s="1"/>
+      <c r="E3" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D3" t="s">
-        <v>15</v>
-      </c>
-      <c r="E3" t="s">
-        <v>13</v>
-      </c>
       <c r="F3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K3" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
     </row>
     <row r="4" ht="25.5" customHeight="1" spans="1:11">
       <c r="A4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>11</v>
-      </c>
-      <c r="C4" t="s">
-        <v>16</v>
-      </c>
-      <c r="D4" t="s">
-        <v>16</v>
-      </c>
-      <c r="E4" t="s">
-        <v>17</v>
+        <v>14</v>
+      </c>
+      <c r="C4"/>
+      <c r="D4" s="1"/>
+      <c r="E4" s="1" t="s">
+        <v>15</v>
       </c>
       <c r="F4" t="s">
         <v>18</v>
@@ -1735,59 +1722,55 @@
         <v>18</v>
       </c>
       <c r="K4" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
     </row>
     <row r="5" ht="25.5" customHeight="1" spans="1:11">
       <c r="A5">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C5" t="s">
-        <v>16</v>
-      </c>
-      <c r="D5" t="s">
-        <v>16</v>
-      </c>
-      <c r="E5" t="s">
-        <v>17</v>
+        <v>19</v>
+      </c>
+      <c r="D5" s="1"/>
+      <c r="E5" s="1" t="s">
+        <v>20</v>
       </c>
       <c r="F5" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="G5" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="H5" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="I5" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="J5" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="K5" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
     </row>
     <row r="6" ht="25.5" customHeight="1" spans="1:11">
       <c r="A6">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C6" t="s">
+        <v>19</v>
+      </c>
+      <c r="D6" s="1"/>
+      <c r="E6" s="1" t="s">
         <v>20</v>
-      </c>
-      <c r="D6" t="s">
-        <v>21</v>
-      </c>
-      <c r="E6" t="s">
-        <v>17</v>
       </c>
       <c r="F6" t="s">
         <v>22</v>
@@ -1805,121 +1788,127 @@
         <v>22</v>
       </c>
       <c r="K6" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
     </row>
     <row r="7" ht="25.5" customHeight="1" spans="1:11">
       <c r="A7">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C7" t="s">
+        <v>23</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="E7" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="D7" t="s">
-        <v>21</v>
-      </c>
-      <c r="E7" t="s">
-        <v>17</v>
-      </c>
       <c r="F7" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="G7" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="H7" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="I7" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="J7" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="K7" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
     </row>
     <row r="8" ht="25.5" customHeight="1" spans="1:11">
       <c r="A8">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C8" t="s">
+        <v>23</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="E8" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="D8" t="s">
-        <v>21</v>
-      </c>
-      <c r="E8" t="s">
-        <v>13</v>
-      </c>
       <c r="F8" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="G8" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="H8" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="I8" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="J8" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="K8" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
     </row>
     <row r="9" ht="25.5" customHeight="1" spans="1:11">
       <c r="A9">
-        <v>151</v>
+        <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C9" t="s">
-        <v>25</v>
-      </c>
-      <c r="D9" t="s">
-        <v>26</v>
-      </c>
-      <c r="E9" t="s">
-        <v>17</v>
+        <v>23</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>15</v>
       </c>
       <c r="F9" t="s">
         <v>27</v>
       </c>
-      <c r="G9"/>
-      <c r="H9"/>
-      <c r="I9"/>
-      <c r="J9"/>
+      <c r="G9" t="s">
+        <v>27</v>
+      </c>
+      <c r="H9" t="s">
+        <v>27</v>
+      </c>
+      <c r="I9" t="s">
+        <v>27</v>
+      </c>
+      <c r="J9" t="s">
+        <v>27</v>
+      </c>
       <c r="K9" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
     </row>
     <row r="10" ht="25.5" customHeight="1" spans="1:11">
       <c r="A10">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="B10" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C10" t="s">
-        <v>25</v>
-      </c>
-      <c r="D10" t="s">
         <v>28</v>
       </c>
-      <c r="E10" t="s">
-        <v>17</v>
+      <c r="D10" s="1"/>
+      <c r="E10" s="1" t="s">
+        <v>20</v>
       </c>
       <c r="F10" t="s">
         <v>29</v>
@@ -1929,58 +1918,46 @@
       <c r="I10"/>
       <c r="J10"/>
       <c r="K10" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
     </row>
     <row r="11" ht="25.5" customHeight="1" spans="1:11">
       <c r="A11">
-        <v>8</v>
+        <v>152</v>
       </c>
       <c r="B11" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C11" t="s">
+        <v>28</v>
+      </c>
+      <c r="D11" s="1"/>
+      <c r="E11" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="F11" t="s">
         <v>30</v>
       </c>
-      <c r="D11" t="s">
-        <v>31</v>
-      </c>
-      <c r="E11" t="s">
-        <v>32</v>
-      </c>
-      <c r="F11" t="s">
-        <v>31</v>
-      </c>
-      <c r="G11" t="s">
-        <v>31</v>
-      </c>
-      <c r="H11" t="s">
-        <v>31</v>
-      </c>
-      <c r="I11" t="s">
-        <v>31</v>
-      </c>
-      <c r="J11" t="s">
-        <v>31</v>
-      </c>
+      <c r="G11"/>
+      <c r="H11"/>
+      <c r="I11"/>
+      <c r="J11"/>
       <c r="K11" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
     </row>
     <row r="12" ht="25.5" customHeight="1" spans="1:11">
       <c r="A12">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B12" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C12" t="s">
-        <v>30</v>
-      </c>
-      <c r="D12" t="s">
-        <v>33</v>
-      </c>
-      <c r="E12" t="s">
+        <v>31</v>
+      </c>
+      <c r="D12" s="1"/>
+      <c r="E12" s="1" t="s">
         <v>32</v>
       </c>
       <c r="F12" t="s">
@@ -1999,23 +1976,21 @@
         <v>33</v>
       </c>
       <c r="K12" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
     </row>
     <row r="13" ht="25.5" customHeight="1" spans="1:11">
       <c r="A13">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B13" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C13" t="s">
-        <v>30</v>
-      </c>
-      <c r="D13" t="s">
-        <v>34</v>
-      </c>
-      <c r="E13" t="s">
+        <v>31</v>
+      </c>
+      <c r="D13" s="1"/>
+      <c r="E13" s="1" t="s">
         <v>32</v>
       </c>
       <c r="F13" t="s">
@@ -2034,23 +2009,21 @@
         <v>34</v>
       </c>
       <c r="K13" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
     </row>
     <row r="14" ht="25.5" customHeight="1" spans="1:11">
       <c r="A14">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B14" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C14" t="s">
-        <v>30</v>
-      </c>
-      <c r="D14" t="s">
-        <v>35</v>
-      </c>
-      <c r="E14" t="s">
+        <v>31</v>
+      </c>
+      <c r="D14" s="1"/>
+      <c r="E14" s="1" t="s">
         <v>32</v>
       </c>
       <c r="F14" t="s">
@@ -2069,23 +2042,21 @@
         <v>35</v>
       </c>
       <c r="K14" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
     </row>
     <row r="15" ht="25.5" customHeight="1" spans="1:11">
       <c r="A15">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B15" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C15" t="s">
-        <v>30</v>
-      </c>
-      <c r="D15" t="s">
-        <v>36</v>
-      </c>
-      <c r="E15" t="s">
+        <v>31</v>
+      </c>
+      <c r="D15" s="1"/>
+      <c r="E15" s="1" t="s">
         <v>32</v>
       </c>
       <c r="F15" t="s">
@@ -2104,59 +2075,55 @@
         <v>36</v>
       </c>
       <c r="K15" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
     </row>
     <row r="16" ht="25.5" customHeight="1" spans="1:11">
       <c r="A16">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B16" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C16" t="s">
+        <v>31</v>
+      </c>
+      <c r="D16" s="1"/>
+      <c r="E16" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="F16" t="s">
         <v>37</v>
       </c>
-      <c r="D16" t="s">
-        <v>38</v>
-      </c>
-      <c r="E16" t="s">
-        <v>17</v>
-      </c>
-      <c r="F16" t="s">
-        <v>38</v>
-      </c>
       <c r="G16" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="H16" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="I16" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="J16" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="K16" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
     </row>
     <row r="17" ht="25.5" customHeight="1" spans="1:11">
       <c r="A17">
+        <v>13</v>
+      </c>
+      <c r="B17" t="s">
         <v>14</v>
       </c>
-      <c r="B17" t="s">
-        <v>11</v>
-      </c>
       <c r="C17" t="s">
-        <v>37</v>
-      </c>
-      <c r="D17" t="s">
-        <v>39</v>
-      </c>
-      <c r="E17" t="s">
-        <v>13</v>
+        <v>38</v>
+      </c>
+      <c r="D17" s="1"/>
+      <c r="E17" s="1" t="s">
+        <v>20</v>
       </c>
       <c r="F17" t="s">
         <v>39</v>
@@ -2174,24 +2141,22 @@
         <v>39</v>
       </c>
       <c r="K17" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
     </row>
     <row r="18" ht="25.5" customHeight="1" spans="1:11">
       <c r="A18">
+        <v>14</v>
+      </c>
+      <c r="B18" t="s">
+        <v>14</v>
+      </c>
+      <c r="C18" t="s">
+        <v>38</v>
+      </c>
+      <c r="D18" s="1"/>
+      <c r="E18" s="1" t="s">
         <v>15</v>
-      </c>
-      <c r="B18" t="s">
-        <v>11</v>
-      </c>
-      <c r="C18" t="s">
-        <v>37</v>
-      </c>
-      <c r="D18" t="s">
-        <v>40</v>
-      </c>
-      <c r="E18" t="s">
-        <v>17</v>
       </c>
       <c r="F18" t="s">
         <v>40</v>
@@ -2209,24 +2174,22 @@
         <v>40</v>
       </c>
       <c r="K18" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
     </row>
     <row r="19" ht="25.5" customHeight="1" spans="1:11">
       <c r="A19">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B19" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C19" t="s">
-        <v>37</v>
-      </c>
-      <c r="D19" t="s">
-        <v>41</v>
-      </c>
-      <c r="E19" t="s">
-        <v>42</v>
+        <v>38</v>
+      </c>
+      <c r="D19" s="1"/>
+      <c r="E19" s="1" t="s">
+        <v>20</v>
       </c>
       <c r="F19" t="s">
         <v>41</v>
@@ -2244,3202 +2207,3200 @@
         <v>41</v>
       </c>
       <c r="K19" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
     </row>
     <row r="20" ht="25.5" customHeight="1" spans="1:11">
       <c r="A20">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B20" t="s">
+        <v>14</v>
+      </c>
+      <c r="C20" t="s">
+        <v>38</v>
+      </c>
+      <c r="D20" s="1"/>
+      <c r="E20" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="F20" t="s">
         <v>43</v>
       </c>
-      <c r="C20" t="s">
-        <v>44</v>
-      </c>
-      <c r="D20" t="s">
-        <v>45</v>
-      </c>
-      <c r="E20" t="s">
-        <v>46</v>
-      </c>
-      <c r="F20" t="s">
-        <v>47</v>
-      </c>
       <c r="G20" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="H20" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="I20" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="J20" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="K20" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
     </row>
     <row r="21" ht="25.5" customHeight="1" spans="1:11">
       <c r="A21">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B21" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C21" t="s">
-        <v>44</v>
-      </c>
-      <c r="D21" t="s">
         <v>45</v>
       </c>
-      <c r="E21" t="s">
+      <c r="D21" s="1" t="s">
         <v>46</v>
       </c>
+      <c r="E21" s="1" t="s">
+        <v>45</v>
+      </c>
       <c r="F21" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="G21" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="H21" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="I21" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="J21" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="K21" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
     </row>
     <row r="22" ht="25.5" customHeight="1" spans="1:11">
       <c r="A22">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B22" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C22" t="s">
-        <v>44</v>
-      </c>
-      <c r="D22" t="s">
         <v>45</v>
       </c>
-      <c r="E22" t="s">
+      <c r="D22" s="1" t="s">
         <v>46</v>
       </c>
+      <c r="E22" s="1" t="s">
+        <v>45</v>
+      </c>
       <c r="F22" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="G22" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="H22" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="I22" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="J22" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="K22" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
     </row>
     <row r="23" ht="25.5" customHeight="1" spans="1:11">
       <c r="A23">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B23" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C23" t="s">
-        <v>44</v>
-      </c>
-      <c r="D23" t="s">
         <v>45</v>
       </c>
-      <c r="E23" t="s">
+      <c r="D23" s="1" t="s">
         <v>46</v>
       </c>
+      <c r="E23" s="1" t="s">
+        <v>45</v>
+      </c>
       <c r="F23" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G23" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="H23" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="I23" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="J23" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="K23" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
     </row>
     <row r="24" ht="25.5" customHeight="1" spans="1:11">
       <c r="A24">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B24" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C24" t="s">
-        <v>44</v>
-      </c>
-      <c r="D24" t="s">
         <v>45</v>
       </c>
-      <c r="E24" t="s">
+      <c r="D24" s="1" t="s">
         <v>46</v>
       </c>
+      <c r="E24" s="1" t="s">
+        <v>45</v>
+      </c>
       <c r="F24" t="s">
-        <v>51</v>
-      </c>
-      <c r="G24"/>
-      <c r="H24"/>
-      <c r="I24"/>
-      <c r="J24"/>
+        <v>50</v>
+      </c>
+      <c r="G24" t="s">
+        <v>50</v>
+      </c>
+      <c r="H24" t="s">
+        <v>50</v>
+      </c>
+      <c r="I24" t="s">
+        <v>50</v>
+      </c>
+      <c r="J24" t="s">
+        <v>50</v>
+      </c>
       <c r="K24" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
     </row>
     <row r="25" ht="25.5" customHeight="1" spans="1:11">
       <c r="A25">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B25" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C25" t="s">
-        <v>44</v>
-      </c>
-      <c r="D25" t="s">
         <v>45</v>
       </c>
-      <c r="E25" t="s">
-        <v>52</v>
+      <c r="D25" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="E25" s="1" t="s">
+        <v>45</v>
       </c>
       <c r="F25" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="G25"/>
       <c r="H25"/>
       <c r="I25"/>
       <c r="J25"/>
       <c r="K25" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
     </row>
     <row r="26" ht="25.5" customHeight="1" spans="1:11">
       <c r="A26">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B26" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C26" t="s">
-        <v>44</v>
-      </c>
-      <c r="D26" t="s">
-        <v>45</v>
-      </c>
-      <c r="E26" t="s">
         <v>52</v>
       </c>
+      <c r="D26" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="E26" s="1" t="s">
+        <v>52</v>
+      </c>
       <c r="F26" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G26"/>
       <c r="H26"/>
       <c r="I26"/>
       <c r="J26"/>
       <c r="K26" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
     </row>
     <row r="27" ht="25.5" customHeight="1" spans="1:11">
       <c r="A27">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B27" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C27" t="s">
-        <v>44</v>
-      </c>
-      <c r="D27" t="s">
-        <v>45</v>
-      </c>
-      <c r="E27" t="s">
         <v>52</v>
       </c>
+      <c r="D27" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="E27" s="1" t="s">
+        <v>52</v>
+      </c>
       <c r="F27" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="G27"/>
       <c r="H27"/>
       <c r="I27"/>
       <c r="J27"/>
       <c r="K27" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
     </row>
     <row r="28" ht="25.5" customHeight="1" spans="1:11">
       <c r="A28">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B28" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C28" t="s">
-        <v>44</v>
-      </c>
-      <c r="D28" t="s">
-        <v>45</v>
-      </c>
-      <c r="E28" t="s">
         <v>52</v>
       </c>
+      <c r="D28" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="E28" s="1" t="s">
+        <v>52</v>
+      </c>
       <c r="F28" t="s">
-        <v>56</v>
-      </c>
-      <c r="G28" t="s">
-        <v>56</v>
-      </c>
-      <c r="H28" t="s">
-        <v>56</v>
-      </c>
-      <c r="I28" t="s">
-        <v>56</v>
-      </c>
-      <c r="J28" t="s">
-        <v>56</v>
-      </c>
+        <v>55</v>
+      </c>
+      <c r="G28"/>
+      <c r="H28"/>
+      <c r="I28"/>
+      <c r="J28"/>
       <c r="K28" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
     </row>
     <row r="29" ht="25.5" customHeight="1" spans="1:11">
       <c r="A29">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B29" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C29" t="s">
-        <v>44</v>
-      </c>
-      <c r="D29" t="s">
-        <v>45</v>
-      </c>
-      <c r="E29" t="s">
         <v>52</v>
       </c>
+      <c r="D29" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="E29" s="1" t="s">
+        <v>52</v>
+      </c>
       <c r="F29" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G29" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="H29" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="I29" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="J29" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="K29" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
     </row>
     <row r="30" ht="25.5" customHeight="1" spans="1:11">
       <c r="A30">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B30" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C30" t="s">
-        <v>44</v>
-      </c>
-      <c r="D30" t="s">
-        <v>45</v>
-      </c>
-      <c r="E30" t="s">
         <v>52</v>
       </c>
+      <c r="D30" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="E30" s="1" t="s">
+        <v>52</v>
+      </c>
       <c r="F30" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G30" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="H30" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="I30" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="J30" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="K30" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
     </row>
     <row r="31" ht="25.5" customHeight="1" spans="1:11">
       <c r="A31">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B31" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C31" t="s">
-        <v>44</v>
-      </c>
-      <c r="D31" t="s">
-        <v>45</v>
-      </c>
-      <c r="E31" t="s">
-        <v>59</v>
+        <v>52</v>
+      </c>
+      <c r="D31" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="E31" s="1" t="s">
+        <v>52</v>
       </c>
       <c r="F31" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="G31" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="H31" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="I31" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="J31" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="K31" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
     </row>
     <row r="32" ht="25.5" customHeight="1" spans="1:11">
       <c r="A32">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B32" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C32" t="s">
-        <v>44</v>
-      </c>
-      <c r="D32" t="s">
-        <v>45</v>
-      </c>
-      <c r="E32" t="s">
         <v>59</v>
       </c>
+      <c r="D32" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="E32" s="1" t="s">
+        <v>59</v>
+      </c>
       <c r="F32" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="G32" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="H32" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="I32" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="J32" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="K32" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
     </row>
     <row r="33" ht="25.5" customHeight="1" spans="1:11">
       <c r="A33">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B33" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C33" t="s">
-        <v>44</v>
-      </c>
-      <c r="D33" t="s">
-        <v>45</v>
-      </c>
-      <c r="E33" t="s">
         <v>59</v>
       </c>
+      <c r="D33" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="E33" s="1" t="s">
+        <v>59</v>
+      </c>
       <c r="F33" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="G33" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="H33" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="I33" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="J33" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="K33" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
     </row>
     <row r="34" ht="25.5" customHeight="1" spans="1:11">
       <c r="A34">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B34" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C34" t="s">
-        <v>44</v>
-      </c>
-      <c r="D34" t="s">
-        <v>45</v>
-      </c>
-      <c r="E34" t="s">
         <v>59</v>
       </c>
+      <c r="D34" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="E34" s="1" t="s">
+        <v>59</v>
+      </c>
       <c r="F34" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="G34" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="H34" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="I34" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="J34" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="K34" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
     </row>
     <row r="35" ht="25.5" customHeight="1" spans="1:11">
       <c r="A35">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B35" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C35" t="s">
-        <v>44</v>
-      </c>
-      <c r="D35" t="s">
-        <v>45</v>
-      </c>
-      <c r="E35" t="s">
-        <v>64</v>
+        <v>59</v>
+      </c>
+      <c r="D35" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="E35" s="1" t="s">
+        <v>59</v>
       </c>
       <c r="F35" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="G35" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="H35" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="I35" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="J35" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="K35" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
     </row>
     <row r="36" ht="25.5" customHeight="1" spans="1:11">
       <c r="A36">
-        <v>148</v>
+        <v>32</v>
       </c>
       <c r="B36" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C36" t="s">
-        <v>44</v>
-      </c>
-      <c r="D36" t="s">
-        <v>66</v>
-      </c>
-      <c r="E36" t="s">
+        <v>64</v>
+      </c>
+      <c r="D36" s="1" t="s">
         <v>46</v>
       </c>
+      <c r="E36" s="1" t="s">
+        <v>64</v>
+      </c>
       <c r="F36" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="G36" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="H36" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="I36" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="J36" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="K36" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
     </row>
     <row r="37" ht="25.5" customHeight="1" spans="1:11">
       <c r="A37">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="B37" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C37" t="s">
-        <v>44</v>
-      </c>
-      <c r="D37" t="s">
+        <v>45</v>
+      </c>
+      <c r="D37" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="E37" t="s">
-        <v>46</v>
+      <c r="E37" s="1" t="s">
+        <v>45</v>
       </c>
       <c r="F37" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G37" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="H37" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="I37" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="J37" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="K37" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
     </row>
     <row r="38" ht="25.5" customHeight="1" spans="1:11">
       <c r="A38">
-        <v>33</v>
+        <v>150</v>
       </c>
       <c r="B38" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C38" t="s">
-        <v>44</v>
-      </c>
-      <c r="D38" t="s">
+        <v>45</v>
+      </c>
+      <c r="D38" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="E38" t="s">
-        <v>46</v>
+      <c r="E38" s="1" t="s">
+        <v>45</v>
       </c>
       <c r="F38" t="s">
-        <v>69</v>
-      </c>
-      <c r="G38"/>
-      <c r="H38"/>
-      <c r="I38"/>
-      <c r="J38"/>
+        <v>68</v>
+      </c>
+      <c r="G38" t="s">
+        <v>68</v>
+      </c>
+      <c r="H38" t="s">
+        <v>68</v>
+      </c>
+      <c r="I38" t="s">
+        <v>68</v>
+      </c>
+      <c r="J38" t="s">
+        <v>68</v>
+      </c>
       <c r="K38" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
     </row>
     <row r="39" ht="25.5" customHeight="1" spans="1:11">
       <c r="A39">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B39" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C39" t="s">
-        <v>44</v>
-      </c>
-      <c r="D39" t="s">
+        <v>45</v>
+      </c>
+      <c r="D39" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="E39" t="s">
-        <v>46</v>
+      <c r="E39" s="1" t="s">
+        <v>45</v>
       </c>
       <c r="F39" t="s">
-        <v>70</v>
-      </c>
-      <c r="G39" t="s">
-        <v>70</v>
-      </c>
-      <c r="H39" t="s">
-        <v>70</v>
-      </c>
-      <c r="I39" t="s">
-        <v>70</v>
-      </c>
-      <c r="J39" t="s">
-        <v>70</v>
-      </c>
+        <v>69</v>
+      </c>
+      <c r="G39"/>
+      <c r="H39"/>
+      <c r="I39"/>
+      <c r="J39"/>
       <c r="K39" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
     </row>
     <row r="40" ht="25.5" customHeight="1" spans="1:11">
       <c r="A40">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B40" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C40" t="s">
-        <v>44</v>
-      </c>
-      <c r="D40" t="s">
+        <v>45</v>
+      </c>
+      <c r="D40" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="E40" t="s">
-        <v>46</v>
+      <c r="E40" s="1" t="s">
+        <v>45</v>
       </c>
       <c r="F40" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="G40" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="H40" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="I40" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="J40" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="K40" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
     </row>
     <row r="41" ht="25.5" customHeight="1" spans="1:11">
       <c r="A41">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B41" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C41" t="s">
-        <v>44</v>
-      </c>
-      <c r="D41" t="s">
+        <v>45</v>
+      </c>
+      <c r="D41" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="E41" t="s">
-        <v>46</v>
+      <c r="E41" s="1" t="s">
+        <v>45</v>
       </c>
       <c r="F41" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="G41" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="H41" t="s">
-        <v>72</v>
-      </c>
-      <c r="I41"/>
-      <c r="J41"/>
+        <v>71</v>
+      </c>
+      <c r="I41" t="s">
+        <v>71</v>
+      </c>
+      <c r="J41" t="s">
+        <v>71</v>
+      </c>
       <c r="K41" t="s">
-        <v>73</v>
+        <v>17</v>
       </c>
     </row>
     <row r="42" ht="25.5" customHeight="1" spans="1:11">
       <c r="A42">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B42" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C42" t="s">
-        <v>44</v>
-      </c>
-      <c r="D42" t="s">
+        <v>45</v>
+      </c>
+      <c r="D42" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="E42" t="s">
-        <v>52</v>
+      <c r="E42" s="1" t="s">
+        <v>45</v>
       </c>
       <c r="F42" t="s">
-        <v>74</v>
-      </c>
-      <c r="G42"/>
-      <c r="H42"/>
+        <v>72</v>
+      </c>
+      <c r="G42" t="s">
+        <v>72</v>
+      </c>
+      <c r="H42" t="s">
+        <v>72</v>
+      </c>
       <c r="I42"/>
       <c r="J42"/>
       <c r="K42" t="s">
-        <v>14</v>
+        <v>73</v>
       </c>
     </row>
     <row r="43" ht="25.5" customHeight="1" spans="1:11">
       <c r="A43">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B43" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C43" t="s">
-        <v>44</v>
-      </c>
-      <c r="D43" t="s">
+        <v>52</v>
+      </c>
+      <c r="D43" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="E43" t="s">
+      <c r="E43" s="1" t="s">
         <v>52</v>
       </c>
       <c r="F43" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="G43"/>
       <c r="H43"/>
       <c r="I43"/>
       <c r="J43"/>
       <c r="K43" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
     </row>
     <row r="44" ht="25.5" customHeight="1" spans="1:11">
       <c r="A44">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B44" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C44" t="s">
-        <v>44</v>
-      </c>
-      <c r="D44" t="s">
+        <v>52</v>
+      </c>
+      <c r="D44" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="E44" t="s">
+      <c r="E44" s="1" t="s">
         <v>52</v>
       </c>
       <c r="F44" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="G44"/>
       <c r="H44"/>
       <c r="I44"/>
       <c r="J44"/>
       <c r="K44" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
     </row>
     <row r="45" ht="25.5" customHeight="1" spans="1:11">
       <c r="A45">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B45" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C45" t="s">
-        <v>44</v>
-      </c>
-      <c r="D45" t="s">
+        <v>52</v>
+      </c>
+      <c r="D45" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="E45" t="s">
-        <v>59</v>
+      <c r="E45" s="1" t="s">
+        <v>52</v>
       </c>
       <c r="F45" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="G45"/>
       <c r="H45"/>
       <c r="I45"/>
       <c r="J45"/>
       <c r="K45" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
     </row>
     <row r="46" ht="25.5" customHeight="1" spans="1:11">
       <c r="A46">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B46" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C46" t="s">
-        <v>44</v>
-      </c>
-      <c r="D46" t="s">
+        <v>59</v>
+      </c>
+      <c r="D46" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="E46" t="s">
+      <c r="E46" s="1" t="s">
         <v>59</v>
       </c>
       <c r="F46" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="G46"/>
       <c r="H46"/>
       <c r="I46"/>
       <c r="J46"/>
       <c r="K46" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
     </row>
     <row r="47" ht="25.5" customHeight="1" spans="1:11">
       <c r="A47">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B47" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C47" t="s">
-        <v>44</v>
-      </c>
-      <c r="D47" t="s">
+        <v>59</v>
+      </c>
+      <c r="D47" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="E47" t="s">
+      <c r="E47" s="1" t="s">
         <v>59</v>
       </c>
       <c r="F47" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="G47"/>
       <c r="H47"/>
       <c r="I47"/>
       <c r="J47"/>
       <c r="K47" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
     </row>
     <row r="48" ht="25.5" customHeight="1" spans="1:11">
       <c r="A48">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B48" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C48" t="s">
-        <v>44</v>
-      </c>
-      <c r="D48" t="s">
+        <v>59</v>
+      </c>
+      <c r="D48" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="E48" t="s">
+      <c r="E48" s="1" t="s">
         <v>59</v>
       </c>
       <c r="F48" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="G48"/>
       <c r="H48"/>
       <c r="I48"/>
       <c r="J48"/>
       <c r="K48" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
     </row>
     <row r="49" ht="25.5" customHeight="1" spans="1:11">
       <c r="A49">
+        <v>43</v>
+      </c>
+      <c r="B49" t="s">
         <v>44</v>
       </c>
-      <c r="B49" t="s">
-        <v>43</v>
-      </c>
       <c r="C49" t="s">
-        <v>44</v>
-      </c>
-      <c r="D49" t="s">
+        <v>59</v>
+      </c>
+      <c r="D49" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="E49" t="s">
+      <c r="E49" s="1" t="s">
         <v>59</v>
       </c>
       <c r="F49" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="G49"/>
       <c r="H49"/>
       <c r="I49"/>
       <c r="J49"/>
       <c r="K49" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
     </row>
     <row r="50" ht="25.5" customHeight="1" spans="1:11">
       <c r="A50">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B50" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C50" t="s">
-        <v>44</v>
-      </c>
-      <c r="D50" t="s">
+        <v>59</v>
+      </c>
+      <c r="D50" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="E50" t="s">
-        <v>82</v>
+      <c r="E50" s="1" t="s">
+        <v>59</v>
       </c>
       <c r="F50" t="s">
-        <v>83</v>
-      </c>
-      <c r="G50" t="s">
-        <v>83</v>
-      </c>
-      <c r="H50" t="s">
-        <v>83</v>
-      </c>
-      <c r="I50" t="s">
-        <v>83</v>
-      </c>
-      <c r="J50" t="s">
-        <v>83</v>
-      </c>
+        <v>81</v>
+      </c>
+      <c r="G50"/>
+      <c r="H50"/>
+      <c r="I50"/>
+      <c r="J50"/>
       <c r="K50" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
     </row>
     <row r="51" ht="25.5" customHeight="1" spans="1:11">
       <c r="A51">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B51" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C51" t="s">
-        <v>44</v>
-      </c>
-      <c r="D51" t="s">
+        <v>82</v>
+      </c>
+      <c r="D51" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="E51" t="s">
+      <c r="E51" s="1" t="s">
         <v>82</v>
       </c>
       <c r="F51" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="G51" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="H51" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="I51" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="J51" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="K51" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
     </row>
     <row r="52" ht="25.5" customHeight="1" spans="1:11">
       <c r="A52">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B52" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C52" t="s">
-        <v>44</v>
-      </c>
-      <c r="D52" t="s">
+        <v>82</v>
+      </c>
+      <c r="D52" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="E52" t="s">
+      <c r="E52" s="1" t="s">
         <v>82</v>
       </c>
       <c r="F52" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="G52" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="H52" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="I52" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="J52" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="K52" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
     </row>
     <row r="53" ht="25.5" customHeight="1" spans="1:11">
       <c r="A53">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B53" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C53" t="s">
-        <v>44</v>
-      </c>
-      <c r="D53" t="s">
+        <v>82</v>
+      </c>
+      <c r="D53" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="E53" t="s">
+      <c r="E53" s="1" t="s">
         <v>82</v>
       </c>
       <c r="F53" t="s">
-        <v>86</v>
-      </c>
-      <c r="G53"/>
-      <c r="H53"/>
-      <c r="I53"/>
-      <c r="J53"/>
+        <v>85</v>
+      </c>
+      <c r="G53" t="s">
+        <v>85</v>
+      </c>
+      <c r="H53" t="s">
+        <v>85</v>
+      </c>
+      <c r="I53" t="s">
+        <v>85</v>
+      </c>
+      <c r="J53" t="s">
+        <v>85</v>
+      </c>
       <c r="K53" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
     </row>
     <row r="54" ht="25.5" customHeight="1" spans="1:11">
       <c r="A54">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B54" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C54" t="s">
-        <v>44</v>
-      </c>
-      <c r="D54" t="s">
+        <v>82</v>
+      </c>
+      <c r="D54" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="E54" t="s">
-        <v>64</v>
+      <c r="E54" s="1" t="s">
+        <v>82</v>
       </c>
       <c r="F54" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="G54"/>
       <c r="H54"/>
       <c r="I54"/>
       <c r="J54"/>
       <c r="K54" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
     </row>
     <row r="55" ht="25.5" customHeight="1" spans="1:11">
       <c r="A55">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B55" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C55" t="s">
-        <v>44</v>
-      </c>
-      <c r="D55" t="s">
+        <v>64</v>
+      </c>
+      <c r="D55" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="E55" t="s">
+      <c r="E55" s="1" t="s">
         <v>64</v>
       </c>
       <c r="F55" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="G55"/>
       <c r="H55"/>
       <c r="I55"/>
       <c r="J55"/>
       <c r="K55" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
     </row>
     <row r="56" ht="25.5" customHeight="1" spans="1:11">
       <c r="A56">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B56" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C56" t="s">
-        <v>44</v>
-      </c>
-      <c r="D56" t="s">
+        <v>64</v>
+      </c>
+      <c r="D56" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="E56" t="s">
+      <c r="E56" s="1" t="s">
         <v>64</v>
       </c>
       <c r="F56" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="G56"/>
       <c r="H56"/>
       <c r="I56"/>
       <c r="J56"/>
       <c r="K56" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
     </row>
     <row r="57" ht="25.5" customHeight="1" spans="1:11">
       <c r="A57">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B57" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C57" t="s">
-        <v>44</v>
-      </c>
-      <c r="D57" t="s">
+        <v>64</v>
+      </c>
+      <c r="D57" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="E57" t="s">
+      <c r="E57" s="1" t="s">
         <v>64</v>
       </c>
       <c r="F57" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="G57"/>
       <c r="H57"/>
       <c r="I57"/>
       <c r="J57"/>
       <c r="K57" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
     </row>
     <row r="58" ht="25.5" customHeight="1" spans="1:11">
       <c r="A58">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B58" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C58" t="s">
-        <v>44</v>
-      </c>
-      <c r="D58" t="s">
+        <v>64</v>
+      </c>
+      <c r="D58" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="E58" t="s">
+      <c r="E58" s="1" t="s">
         <v>64</v>
       </c>
       <c r="F58" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="G58"/>
       <c r="H58"/>
       <c r="I58"/>
       <c r="J58"/>
       <c r="K58" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
     </row>
     <row r="59" ht="25.5" customHeight="1" spans="1:11">
       <c r="A59">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B59" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C59" t="s">
-        <v>44</v>
-      </c>
-      <c r="D59" t="s">
+        <v>64</v>
+      </c>
+      <c r="D59" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="E59" t="s">
+      <c r="E59" s="1" t="s">
         <v>64</v>
       </c>
       <c r="F59" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="G59"/>
       <c r="H59"/>
       <c r="I59"/>
       <c r="J59"/>
       <c r="K59" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
     </row>
     <row r="60" ht="25.5" customHeight="1" spans="1:11">
       <c r="A60">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B60" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C60" t="s">
-        <v>44</v>
-      </c>
-      <c r="D60" t="s">
-        <v>93</v>
-      </c>
-      <c r="E60" t="s">
-        <v>94</v>
+        <v>64</v>
+      </c>
+      <c r="D60" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="E60" s="1" t="s">
+        <v>64</v>
       </c>
       <c r="F60" t="s">
-        <v>95</v>
-      </c>
-      <c r="G60" t="s">
-        <v>95</v>
-      </c>
-      <c r="H60" t="s">
-        <v>95</v>
-      </c>
-      <c r="I60" t="s">
-        <v>95</v>
-      </c>
-      <c r="J60" t="s">
-        <v>95</v>
-      </c>
+        <v>92</v>
+      </c>
+      <c r="G60"/>
+      <c r="H60"/>
+      <c r="I60"/>
+      <c r="J60"/>
       <c r="K60" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
     </row>
     <row r="61" ht="25.5" customHeight="1" spans="1:11">
       <c r="A61">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B61" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C61" t="s">
-        <v>96</v>
-      </c>
-      <c r="D61" t="s">
-        <v>45</v>
-      </c>
-      <c r="E61" t="s">
-        <v>46</v>
+        <v>93</v>
+      </c>
+      <c r="D61" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="E61" s="1" t="s">
+        <v>93</v>
       </c>
       <c r="F61" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="G61" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="H61" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="I61" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="J61" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="K61" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
     </row>
     <row r="62" ht="25.5" customHeight="1" spans="1:11">
       <c r="A62">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B62" t="s">
-        <v>43</v>
+        <v>96</v>
       </c>
       <c r="C62" t="s">
-        <v>96</v>
-      </c>
-      <c r="D62" t="s">
         <v>45</v>
       </c>
-      <c r="E62" t="s">
+      <c r="D62" s="1" t="s">
         <v>46</v>
       </c>
+      <c r="E62" s="1" t="s">
+        <v>45</v>
+      </c>
       <c r="F62" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="G62" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="H62" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="I62" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="J62" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="K62" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
     </row>
     <row r="63" ht="25.5" customHeight="1" spans="1:11">
       <c r="A63">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B63" t="s">
-        <v>43</v>
+        <v>96</v>
       </c>
       <c r="C63" t="s">
-        <v>96</v>
-      </c>
-      <c r="D63" t="s">
         <v>45</v>
       </c>
-      <c r="E63" t="s">
+      <c r="D63" s="1" t="s">
         <v>46</v>
       </c>
+      <c r="E63" s="1" t="s">
+        <v>45</v>
+      </c>
       <c r="F63" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="G63" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="H63" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="I63" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="J63" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="K63" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
     </row>
     <row r="64" ht="25.5" customHeight="1" spans="1:11">
       <c r="A64">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B64" t="s">
-        <v>43</v>
+        <v>96</v>
       </c>
       <c r="C64" t="s">
-        <v>96</v>
-      </c>
-      <c r="D64" t="s">
         <v>45</v>
       </c>
-      <c r="E64" t="s">
-        <v>52</v>
+      <c r="D64" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="E64" s="1" t="s">
+        <v>45</v>
       </c>
       <c r="F64" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="G64" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="H64" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="I64" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="J64" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="K64" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
     </row>
     <row r="65" ht="25.5" customHeight="1" spans="1:11">
       <c r="A65">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B65" t="s">
-        <v>43</v>
+        <v>96</v>
       </c>
       <c r="C65" t="s">
-        <v>96</v>
-      </c>
-      <c r="D65" t="s">
-        <v>45</v>
-      </c>
-      <c r="E65" t="s">
-        <v>59</v>
+        <v>52</v>
+      </c>
+      <c r="D65" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="E65" s="1" t="s">
+        <v>52</v>
       </c>
       <c r="F65" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="G65" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="H65" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="I65" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="J65" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="K65" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
     </row>
     <row r="66" ht="25.5" customHeight="1" spans="1:11">
       <c r="A66">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B66" t="s">
-        <v>43</v>
+        <v>96</v>
       </c>
       <c r="C66" t="s">
-        <v>96</v>
-      </c>
-      <c r="D66" t="s">
-        <v>45</v>
-      </c>
-      <c r="E66" t="s">
-        <v>82</v>
+        <v>59</v>
+      </c>
+      <c r="D66" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="E66" s="1" t="s">
+        <v>59</v>
       </c>
       <c r="F66" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="G66" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="H66" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="I66" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="J66" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="K66" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
     </row>
     <row r="67" ht="25.5" customHeight="1" spans="1:11">
       <c r="A67">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B67" t="s">
-        <v>43</v>
+        <v>96</v>
       </c>
       <c r="C67" t="s">
-        <v>96</v>
-      </c>
-      <c r="D67" t="s">
-        <v>45</v>
-      </c>
-      <c r="E67" t="s">
         <v>82</v>
       </c>
+      <c r="D67" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="E67" s="1" t="s">
+        <v>82</v>
+      </c>
       <c r="F67" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="G67" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="H67" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="I67" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="J67" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="K67" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
     </row>
     <row r="68" ht="25.5" customHeight="1" spans="1:11">
       <c r="A68">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B68" t="s">
-        <v>43</v>
+        <v>96</v>
       </c>
       <c r="C68" t="s">
-        <v>96</v>
-      </c>
-      <c r="D68" t="s">
-        <v>66</v>
-      </c>
-      <c r="E68" t="s">
+        <v>82</v>
+      </c>
+      <c r="D68" s="1" t="s">
         <v>46</v>
       </c>
+      <c r="E68" s="1" t="s">
+        <v>82</v>
+      </c>
       <c r="F68" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="G68" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="H68" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="I68" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="J68" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="K68" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
     </row>
     <row r="69" ht="25.5" customHeight="1" spans="1:11">
       <c r="A69">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B69" t="s">
-        <v>43</v>
+        <v>96</v>
       </c>
       <c r="C69" t="s">
-        <v>96</v>
-      </c>
-      <c r="D69" t="s">
+        <v>45</v>
+      </c>
+      <c r="D69" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="E69" t="s">
-        <v>46</v>
+      <c r="E69" s="1" t="s">
+        <v>45</v>
       </c>
       <c r="F69" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="G69" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="H69" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="I69" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="J69" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="K69" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
     </row>
     <row r="70" ht="25.5" customHeight="1" spans="1:11">
       <c r="A70">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B70" t="s">
-        <v>43</v>
+        <v>96</v>
       </c>
       <c r="C70" t="s">
-        <v>96</v>
-      </c>
-      <c r="D70" t="s">
+        <v>45</v>
+      </c>
+      <c r="D70" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="E70" t="s">
-        <v>46</v>
+      <c r="E70" s="1" t="s">
+        <v>45</v>
       </c>
       <c r="F70" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="G70" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="H70" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="I70" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="J70" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="K70" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
     </row>
     <row r="71" ht="25.5" customHeight="1" spans="1:11">
       <c r="A71">
-        <v>154</v>
+        <v>65</v>
       </c>
       <c r="B71" t="s">
-        <v>43</v>
+        <v>96</v>
       </c>
       <c r="C71" t="s">
-        <v>96</v>
-      </c>
-      <c r="D71" t="s">
+        <v>45</v>
+      </c>
+      <c r="D71" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="E71" t="s">
-        <v>46</v>
+      <c r="E71" s="1" t="s">
+        <v>45</v>
       </c>
       <c r="F71" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="G71" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="H71" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="I71" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="J71" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="K71" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
     </row>
     <row r="72" ht="25.5" customHeight="1" spans="1:11">
       <c r="A72">
-        <v>149</v>
+        <v>154</v>
       </c>
       <c r="B72" t="s">
-        <v>43</v>
+        <v>96</v>
       </c>
       <c r="C72" t="s">
-        <v>96</v>
-      </c>
-      <c r="D72" t="s">
+        <v>45</v>
+      </c>
+      <c r="D72" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="E72" t="s">
-        <v>46</v>
+      <c r="E72" s="1" t="s">
+        <v>45</v>
       </c>
       <c r="F72" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="G72" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="H72" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="I72" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="J72" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="K72" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
     </row>
     <row r="73" ht="25.5" customHeight="1" spans="1:11">
       <c r="A73">
+        <v>149</v>
+      </c>
+      <c r="B73" t="s">
+        <v>96</v>
+      </c>
+      <c r="C73" t="s">
+        <v>45</v>
+      </c>
+      <c r="D73" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="B73" t="s">
-        <v>43</v>
-      </c>
-      <c r="C73" t="s">
-        <v>96</v>
-      </c>
-      <c r="D73" t="s">
-        <v>66</v>
-      </c>
-      <c r="E73" t="s">
-        <v>52</v>
+      <c r="E73" s="1" t="s">
+        <v>45</v>
       </c>
       <c r="F73" t="s">
-        <v>109</v>
-      </c>
-      <c r="G73"/>
-      <c r="H73"/>
-      <c r="I73"/>
-      <c r="J73"/>
+        <v>108</v>
+      </c>
+      <c r="G73" t="s">
+        <v>108</v>
+      </c>
+      <c r="H73" t="s">
+        <v>108</v>
+      </c>
+      <c r="I73" t="s">
+        <v>108</v>
+      </c>
+      <c r="J73" t="s">
+        <v>108</v>
+      </c>
       <c r="K73" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
     </row>
     <row r="74" ht="25.5" customHeight="1" spans="1:11">
       <c r="A74">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B74" t="s">
-        <v>43</v>
+        <v>96</v>
       </c>
       <c r="C74" t="s">
-        <v>96</v>
-      </c>
-      <c r="D74" t="s">
+        <v>52</v>
+      </c>
+      <c r="D74" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="E74" t="s">
+      <c r="E74" s="1" t="s">
         <v>52</v>
       </c>
       <c r="F74" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="G74"/>
       <c r="H74"/>
       <c r="I74"/>
       <c r="J74"/>
       <c r="K74" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
     </row>
     <row r="75" ht="25.5" customHeight="1" spans="1:11">
       <c r="A75">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B75" t="s">
-        <v>43</v>
+        <v>96</v>
       </c>
       <c r="C75" t="s">
-        <v>96</v>
-      </c>
-      <c r="D75" t="s">
+        <v>52</v>
+      </c>
+      <c r="D75" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="E75" t="s">
+      <c r="E75" s="1" t="s">
         <v>52</v>
       </c>
       <c r="F75" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="G75"/>
       <c r="H75"/>
       <c r="I75"/>
       <c r="J75"/>
       <c r="K75" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
     </row>
     <row r="76" ht="25.5" customHeight="1" spans="1:11">
       <c r="A76">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B76" t="s">
-        <v>43</v>
+        <v>96</v>
       </c>
       <c r="C76" t="s">
-        <v>96</v>
-      </c>
-      <c r="D76" t="s">
+        <v>52</v>
+      </c>
+      <c r="D76" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="E76" t="s">
-        <v>59</v>
+      <c r="E76" s="1" t="s">
+        <v>52</v>
       </c>
       <c r="F76" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="G76"/>
       <c r="H76"/>
       <c r="I76"/>
       <c r="J76"/>
       <c r="K76" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
     </row>
     <row r="77" ht="25.5" customHeight="1" spans="1:11">
       <c r="A77">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B77" t="s">
-        <v>43</v>
+        <v>96</v>
       </c>
       <c r="C77" t="s">
-        <v>96</v>
-      </c>
-      <c r="D77" t="s">
+        <v>59</v>
+      </c>
+      <c r="D77" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="E77" t="s">
+      <c r="E77" s="1" t="s">
         <v>59</v>
       </c>
       <c r="F77" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="G77"/>
       <c r="H77"/>
       <c r="I77"/>
       <c r="J77"/>
       <c r="K77" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
     </row>
     <row r="78" ht="25.5" customHeight="1" spans="1:11">
       <c r="A78">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B78" t="s">
-        <v>43</v>
+        <v>96</v>
       </c>
       <c r="C78" t="s">
-        <v>96</v>
-      </c>
-      <c r="D78" t="s">
+        <v>59</v>
+      </c>
+      <c r="D78" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="E78" t="s">
-        <v>82</v>
+      <c r="E78" s="1" t="s">
+        <v>59</v>
       </c>
       <c r="F78" t="s">
-        <v>114</v>
-      </c>
-      <c r="G78" t="s">
-        <v>114</v>
-      </c>
-      <c r="H78" t="s">
-        <v>114</v>
-      </c>
-      <c r="I78" t="s">
-        <v>114</v>
-      </c>
-      <c r="J78" t="s">
-        <v>114</v>
-      </c>
+        <v>113</v>
+      </c>
+      <c r="G78"/>
+      <c r="H78"/>
+      <c r="I78"/>
+      <c r="J78"/>
       <c r="K78" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
     </row>
     <row r="79" ht="25.5" customHeight="1" spans="1:11">
       <c r="A79">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B79" t="s">
-        <v>43</v>
+        <v>96</v>
       </c>
       <c r="C79" t="s">
-        <v>96</v>
-      </c>
-      <c r="D79" t="s">
+        <v>82</v>
+      </c>
+      <c r="D79" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="E79" t="s">
+      <c r="E79" s="1" t="s">
         <v>82</v>
       </c>
       <c r="F79" t="s">
-        <v>115</v>
-      </c>
-      <c r="G79"/>
-      <c r="H79"/>
-      <c r="I79"/>
-      <c r="J79"/>
+        <v>114</v>
+      </c>
+      <c r="G79" t="s">
+        <v>114</v>
+      </c>
+      <c r="H79" t="s">
+        <v>114</v>
+      </c>
+      <c r="I79" t="s">
+        <v>114</v>
+      </c>
+      <c r="J79" t="s">
+        <v>114</v>
+      </c>
       <c r="K79" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
     </row>
     <row r="80" ht="25.5" customHeight="1" spans="1:11">
       <c r="A80">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B80" t="s">
-        <v>43</v>
+        <v>96</v>
       </c>
       <c r="C80" t="s">
-        <v>96</v>
-      </c>
-      <c r="D80" t="s">
-        <v>93</v>
-      </c>
-      <c r="E80" t="s">
-        <v>94</v>
+        <v>82</v>
+      </c>
+      <c r="D80" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="E80" s="1" t="s">
+        <v>82</v>
       </c>
       <c r="F80" t="s">
-        <v>116</v>
-      </c>
-      <c r="G80" t="s">
-        <v>116</v>
-      </c>
-      <c r="H80" t="s">
-        <v>116</v>
-      </c>
-      <c r="I80" t="s">
-        <v>116</v>
-      </c>
-      <c r="J80" t="s">
-        <v>116</v>
-      </c>
+        <v>115</v>
+      </c>
+      <c r="G80"/>
+      <c r="H80"/>
+      <c r="I80"/>
+      <c r="J80"/>
       <c r="K80" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
     </row>
     <row r="81" ht="25.5" customHeight="1" spans="1:11">
       <c r="A81">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B81" t="s">
-        <v>43</v>
+        <v>96</v>
       </c>
       <c r="C81" t="s">
-        <v>117</v>
-      </c>
-      <c r="D81" t="s">
-        <v>45</v>
-      </c>
-      <c r="E81" t="s">
-        <v>46</v>
+        <v>93</v>
+      </c>
+      <c r="D81" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="E81" s="1" t="s">
+        <v>93</v>
       </c>
       <c r="F81" t="s">
-        <v>118</v>
-      </c>
-      <c r="G81"/>
-      <c r="H81"/>
-      <c r="I81"/>
-      <c r="J81"/>
+        <v>116</v>
+      </c>
+      <c r="G81" t="s">
+        <v>116</v>
+      </c>
+      <c r="H81" t="s">
+        <v>116</v>
+      </c>
+      <c r="I81" t="s">
+        <v>116</v>
+      </c>
+      <c r="J81" t="s">
+        <v>116</v>
+      </c>
       <c r="K81" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
     </row>
     <row r="82" ht="25.5" customHeight="1" spans="1:11">
       <c r="A82">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B82" t="s">
-        <v>43</v>
+        <v>117</v>
       </c>
       <c r="C82" t="s">
-        <v>117</v>
-      </c>
-      <c r="D82" t="s">
         <v>45</v>
       </c>
-      <c r="E82" t="s">
+      <c r="D82" s="1" t="s">
         <v>46</v>
       </c>
+      <c r="E82" s="1" t="s">
+        <v>45</v>
+      </c>
       <c r="F82" t="s">
-        <v>119</v>
-      </c>
-      <c r="G82" t="s">
-        <v>119</v>
-      </c>
-      <c r="H82" t="s">
-        <v>119</v>
-      </c>
-      <c r="I82" t="s">
-        <v>119</v>
-      </c>
-      <c r="J82" t="s">
-        <v>119</v>
-      </c>
+        <v>118</v>
+      </c>
+      <c r="G82"/>
+      <c r="H82"/>
+      <c r="I82"/>
+      <c r="J82"/>
       <c r="K82" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
     </row>
     <row r="83" ht="25.5" customHeight="1" spans="1:11">
       <c r="A83">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B83" t="s">
-        <v>43</v>
+        <v>117</v>
       </c>
       <c r="C83" t="s">
-        <v>117</v>
-      </c>
-      <c r="D83" t="s">
         <v>45</v>
       </c>
-      <c r="E83" t="s">
+      <c r="D83" s="1" t="s">
         <v>46</v>
       </c>
+      <c r="E83" s="1" t="s">
+        <v>45</v>
+      </c>
       <c r="F83" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="G83" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="H83" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="I83" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="J83" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="K83" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
     </row>
     <row r="84" ht="25.5" customHeight="1" spans="1:11">
       <c r="A84">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B84" t="s">
-        <v>43</v>
+        <v>117</v>
       </c>
       <c r="C84" t="s">
-        <v>117</v>
-      </c>
-      <c r="D84" t="s">
         <v>45</v>
       </c>
-      <c r="E84" t="s">
+      <c r="D84" s="1" t="s">
         <v>46</v>
       </c>
+      <c r="E84" s="1" t="s">
+        <v>45</v>
+      </c>
       <c r="F84" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="G84" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="H84" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="I84" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="J84" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="K84" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
     </row>
     <row r="85" ht="25.5" customHeight="1" spans="1:11">
       <c r="A85">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B85" t="s">
-        <v>43</v>
+        <v>117</v>
       </c>
       <c r="C85" t="s">
-        <v>117</v>
-      </c>
-      <c r="D85" t="s">
         <v>45</v>
       </c>
-      <c r="E85" t="s">
-        <v>52</v>
+      <c r="D85" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="E85" s="1" t="s">
+        <v>45</v>
       </c>
       <c r="F85" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="G85" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="H85" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="I85" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="J85" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="K85" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
     </row>
     <row r="86" ht="25.5" customHeight="1" spans="1:11">
       <c r="A86">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B86" t="s">
-        <v>43</v>
+        <v>117</v>
       </c>
       <c r="C86" t="s">
-        <v>117</v>
-      </c>
-      <c r="D86" t="s">
-        <v>45</v>
-      </c>
-      <c r="E86" t="s">
         <v>52</v>
       </c>
+      <c r="D86" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="E86" s="1" t="s">
+        <v>52</v>
+      </c>
       <c r="F86" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="G86" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="H86" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="I86" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="J86" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="K86" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
     </row>
     <row r="87" ht="25.5" customHeight="1" spans="1:11">
       <c r="A87">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B87" t="s">
-        <v>43</v>
+        <v>117</v>
       </c>
       <c r="C87" t="s">
-        <v>117</v>
-      </c>
-      <c r="D87" t="s">
-        <v>45</v>
-      </c>
-      <c r="E87" t="s">
-        <v>59</v>
+        <v>52</v>
+      </c>
+      <c r="D87" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="E87" s="1" t="s">
+        <v>52</v>
       </c>
       <c r="F87" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="G87" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="H87" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="I87" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="J87" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="K87" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
     </row>
     <row r="88" ht="25.5" customHeight="1" spans="1:11">
       <c r="A88">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B88" t="s">
-        <v>43</v>
+        <v>117</v>
       </c>
       <c r="C88" t="s">
-        <v>117</v>
-      </c>
-      <c r="D88" t="s">
-        <v>45</v>
-      </c>
-      <c r="E88" t="s">
         <v>59</v>
       </c>
+      <c r="D88" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="E88" s="1" t="s">
+        <v>59</v>
+      </c>
       <c r="F88" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="G88" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="H88" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="I88" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="J88" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="K88" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
     </row>
     <row r="89" ht="25.5" customHeight="1" spans="1:11">
       <c r="A89">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B89" t="s">
-        <v>43</v>
+        <v>117</v>
       </c>
       <c r="C89" t="s">
-        <v>117</v>
-      </c>
-      <c r="D89" t="s">
-        <v>45</v>
-      </c>
-      <c r="E89" t="s">
-        <v>82</v>
+        <v>59</v>
+      </c>
+      <c r="D89" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="E89" s="1" t="s">
+        <v>59</v>
       </c>
       <c r="F89" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="G89" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="H89" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="I89" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="J89" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="K89" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
     </row>
     <row r="90" ht="25.5" customHeight="1" spans="1:11">
       <c r="A90">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B90" t="s">
-        <v>43</v>
+        <v>117</v>
       </c>
       <c r="C90" t="s">
-        <v>117</v>
-      </c>
-      <c r="D90" t="s">
-        <v>66</v>
-      </c>
-      <c r="E90" t="s">
         <v>82</v>
       </c>
+      <c r="D90" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="E90" s="1" t="s">
+        <v>82</v>
+      </c>
       <c r="F90" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="G90" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="H90" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="I90" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="J90" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="K90" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
     </row>
     <row r="91" ht="25.5" customHeight="1" spans="1:11">
       <c r="A91">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B91" t="s">
-        <v>43</v>
+        <v>117</v>
       </c>
       <c r="C91" t="s">
-        <v>117</v>
-      </c>
-      <c r="D91" t="s">
-        <v>45</v>
-      </c>
-      <c r="E91" t="s">
-        <v>64</v>
+        <v>82</v>
+      </c>
+      <c r="D91" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="E91" s="1" t="s">
+        <v>82</v>
       </c>
       <c r="F91" t="s">
-        <v>128</v>
-      </c>
-      <c r="G91"/>
-      <c r="H91"/>
-      <c r="I91"/>
-      <c r="J91"/>
+        <v>127</v>
+      </c>
+      <c r="G91" t="s">
+        <v>127</v>
+      </c>
+      <c r="H91" t="s">
+        <v>127</v>
+      </c>
+      <c r="I91" t="s">
+        <v>127</v>
+      </c>
+      <c r="J91" t="s">
+        <v>127</v>
+      </c>
       <c r="K91" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
     </row>
     <row r="92" ht="25.5" customHeight="1" spans="1:11">
       <c r="A92">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B92" t="s">
-        <v>43</v>
+        <v>117</v>
       </c>
       <c r="C92" t="s">
-        <v>117</v>
-      </c>
-      <c r="D92" t="s">
-        <v>66</v>
-      </c>
-      <c r="E92" t="s">
+        <v>64</v>
+      </c>
+      <c r="D92" s="1" t="s">
         <v>46</v>
       </c>
+      <c r="E92" s="1" t="s">
+        <v>64</v>
+      </c>
       <c r="F92" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="G92"/>
       <c r="H92"/>
       <c r="I92"/>
       <c r="J92"/>
       <c r="K92" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
     </row>
     <row r="93" ht="25.5" customHeight="1" spans="1:11">
       <c r="A93">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B93" t="s">
-        <v>43</v>
+        <v>117</v>
       </c>
       <c r="C93" t="s">
-        <v>117</v>
-      </c>
-      <c r="D93" t="s">
+        <v>45</v>
+      </c>
+      <c r="D93" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="E93" t="s">
-        <v>46</v>
+      <c r="E93" s="1" t="s">
+        <v>45</v>
       </c>
       <c r="F93" t="s">
-        <v>130</v>
-      </c>
-      <c r="G93" t="s">
-        <v>130</v>
-      </c>
-      <c r="H93" t="s">
-        <v>130</v>
-      </c>
-      <c r="I93" t="s">
-        <v>130</v>
-      </c>
-      <c r="J93" t="s">
-        <v>130</v>
-      </c>
+        <v>129</v>
+      </c>
+      <c r="G93"/>
+      <c r="H93"/>
+      <c r="I93"/>
+      <c r="J93"/>
       <c r="K93" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
     </row>
     <row r="94" ht="25.5" customHeight="1" spans="1:11">
       <c r="A94">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B94" t="s">
-        <v>43</v>
+        <v>117</v>
       </c>
       <c r="C94" t="s">
-        <v>117</v>
-      </c>
-      <c r="D94" t="s">
+        <v>45</v>
+      </c>
+      <c r="D94" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="E94" t="s">
-        <v>46</v>
+      <c r="E94" s="1" t="s">
+        <v>45</v>
       </c>
       <c r="F94" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="G94" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="H94" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="I94" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="J94" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="K94" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
     </row>
     <row r="95" ht="25.5" customHeight="1" spans="1:11">
       <c r="A95">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B95" t="s">
-        <v>43</v>
+        <v>117</v>
       </c>
       <c r="C95" t="s">
-        <v>117</v>
-      </c>
-      <c r="D95" t="s">
+        <v>45</v>
+      </c>
+      <c r="D95" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="E95" t="s">
-        <v>46</v>
+      <c r="E95" s="1" t="s">
+        <v>45</v>
       </c>
       <c r="F95" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="G95" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="H95" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="I95" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="J95" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="K95" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
     </row>
     <row r="96" ht="25.5" customHeight="1" spans="1:11">
       <c r="A96">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B96" t="s">
-        <v>43</v>
+        <v>117</v>
       </c>
       <c r="C96" t="s">
-        <v>117</v>
-      </c>
-      <c r="D96" t="s">
+        <v>45</v>
+      </c>
+      <c r="D96" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="E96" t="s">
-        <v>46</v>
+      <c r="E96" s="1" t="s">
+        <v>45</v>
       </c>
       <c r="F96" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="G96" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="H96" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="I96" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="J96" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="K96" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
     </row>
     <row r="97" ht="25.5" customHeight="1" spans="1:11">
       <c r="A97">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B97" t="s">
-        <v>43</v>
+        <v>117</v>
       </c>
       <c r="C97" t="s">
-        <v>117</v>
-      </c>
-      <c r="D97" t="s">
+        <v>45</v>
+      </c>
+      <c r="D97" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="E97" t="s">
-        <v>46</v>
+      <c r="E97" s="1" t="s">
+        <v>45</v>
       </c>
       <c r="F97" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="G97" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="H97" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="I97" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="J97" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="K97" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
     </row>
     <row r="98" ht="25.5" customHeight="1" spans="1:11">
       <c r="A98">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B98" t="s">
-        <v>43</v>
+        <v>117</v>
       </c>
       <c r="C98" t="s">
-        <v>117</v>
-      </c>
-      <c r="D98" t="s">
+        <v>45</v>
+      </c>
+      <c r="D98" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="E98" t="s">
-        <v>52</v>
+      <c r="E98" s="1" t="s">
+        <v>45</v>
       </c>
       <c r="F98" t="s">
-        <v>135</v>
-      </c>
-      <c r="G98"/>
-      <c r="H98"/>
-      <c r="I98"/>
-      <c r="J98"/>
+        <v>134</v>
+      </c>
+      <c r="G98" t="s">
+        <v>134</v>
+      </c>
+      <c r="H98" t="s">
+        <v>134</v>
+      </c>
+      <c r="I98" t="s">
+        <v>134</v>
+      </c>
+      <c r="J98" t="s">
+        <v>134</v>
+      </c>
       <c r="K98" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
     </row>
     <row r="99" ht="25.5" customHeight="1" spans="1:11">
       <c r="A99">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B99" t="s">
-        <v>43</v>
+        <v>117</v>
       </c>
       <c r="C99" t="s">
-        <v>117</v>
-      </c>
-      <c r="D99" t="s">
+        <v>52</v>
+      </c>
+      <c r="D99" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="E99" t="s">
+      <c r="E99" s="1" t="s">
         <v>52</v>
       </c>
       <c r="F99" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="G99"/>
       <c r="H99"/>
       <c r="I99"/>
       <c r="J99"/>
       <c r="K99" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
     </row>
     <row r="100" ht="25.5" customHeight="1" spans="1:11">
       <c r="A100">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B100" t="s">
-        <v>43</v>
+        <v>117</v>
       </c>
       <c r="C100" t="s">
-        <v>117</v>
-      </c>
-      <c r="D100" t="s">
+        <v>52</v>
+      </c>
+      <c r="D100" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="E100" t="s">
+      <c r="E100" s="1" t="s">
         <v>52</v>
       </c>
       <c r="F100" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="G100"/>
       <c r="H100"/>
       <c r="I100"/>
       <c r="J100"/>
       <c r="K100" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
     </row>
     <row r="101" ht="25.5" customHeight="1" spans="1:11">
       <c r="A101">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B101" t="s">
-        <v>43</v>
+        <v>117</v>
       </c>
       <c r="C101" t="s">
-        <v>117</v>
-      </c>
-      <c r="D101" t="s">
+        <v>52</v>
+      </c>
+      <c r="D101" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="E101" t="s">
+      <c r="E101" s="1" t="s">
         <v>52</v>
       </c>
       <c r="F101" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="G101"/>
       <c r="H101"/>
       <c r="I101"/>
       <c r="J101"/>
       <c r="K101" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
     </row>
     <row r="102" ht="25.5" customHeight="1" spans="1:11">
       <c r="A102">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B102" t="s">
-        <v>43</v>
+        <v>117</v>
       </c>
       <c r="C102" t="s">
-        <v>117</v>
-      </c>
-      <c r="D102" t="s">
+        <v>52</v>
+      </c>
+      <c r="D102" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="E102" t="s">
+      <c r="E102" s="1" t="s">
         <v>52</v>
       </c>
       <c r="F102" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="G102"/>
       <c r="H102"/>
       <c r="I102"/>
       <c r="J102"/>
       <c r="K102" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
     </row>
     <row r="103" ht="25.5" customHeight="1" spans="1:11">
       <c r="A103">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B103" t="s">
-        <v>43</v>
+        <v>117</v>
       </c>
       <c r="C103" t="s">
-        <v>117</v>
-      </c>
-      <c r="D103" t="s">
+        <v>52</v>
+      </c>
+      <c r="D103" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="E103" t="s">
+      <c r="E103" s="1" t="s">
         <v>52</v>
       </c>
       <c r="F103" t="s">
-        <v>140</v>
-      </c>
-      <c r="G103" t="s">
-        <v>140</v>
-      </c>
-      <c r="H103" t="s">
-        <v>140</v>
-      </c>
-      <c r="I103" t="s">
-        <v>140</v>
-      </c>
-      <c r="J103" t="s">
-        <v>140</v>
-      </c>
+        <v>139</v>
+      </c>
+      <c r="G103"/>
+      <c r="H103"/>
+      <c r="I103"/>
+      <c r="J103"/>
       <c r="K103" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
     </row>
     <row r="104" ht="25.5" customHeight="1" spans="1:11">
       <c r="A104">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B104" t="s">
-        <v>43</v>
+        <v>117</v>
       </c>
       <c r="C104" t="s">
-        <v>117</v>
-      </c>
-      <c r="D104" t="s">
+        <v>52</v>
+      </c>
+      <c r="D104" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="E104" t="s">
+      <c r="E104" s="1" t="s">
         <v>52</v>
       </c>
       <c r="F104" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="G104" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="H104" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="I104" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="J104" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="K104" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
     </row>
     <row r="105" ht="25.5" customHeight="1" spans="1:11">
       <c r="A105">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B105" t="s">
-        <v>43</v>
+        <v>117</v>
       </c>
       <c r="C105" t="s">
-        <v>117</v>
-      </c>
-      <c r="D105" t="s">
+        <v>52</v>
+      </c>
+      <c r="D105" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="E105" t="s">
+      <c r="E105" s="1" t="s">
         <v>52</v>
       </c>
       <c r="F105" t="s">
-        <v>142</v>
-      </c>
-      <c r="G105"/>
-      <c r="H105"/>
-      <c r="I105"/>
-      <c r="J105"/>
+        <v>141</v>
+      </c>
+      <c r="G105" t="s">
+        <v>141</v>
+      </c>
+      <c r="H105" t="s">
+        <v>141</v>
+      </c>
+      <c r="I105" t="s">
+        <v>141</v>
+      </c>
+      <c r="J105" t="s">
+        <v>141</v>
+      </c>
       <c r="K105" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
     </row>
     <row r="106" ht="25.5" customHeight="1" spans="1:11">
       <c r="A106">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B106" t="s">
-        <v>43</v>
+        <v>117</v>
       </c>
       <c r="C106" t="s">
-        <v>117</v>
-      </c>
-      <c r="D106" t="s">
+        <v>52</v>
+      </c>
+      <c r="D106" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="E106" t="s">
+      <c r="E106" s="1" t="s">
         <v>52</v>
       </c>
       <c r="F106" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="G106"/>
       <c r="H106"/>
       <c r="I106"/>
       <c r="J106"/>
       <c r="K106" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
     </row>
     <row r="107" ht="25.5" customHeight="1" spans="1:11">
       <c r="A107">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B107" t="s">
-        <v>43</v>
+        <v>117</v>
       </c>
       <c r="C107" t="s">
-        <v>117</v>
-      </c>
-      <c r="D107" t="s">
+        <v>52</v>
+      </c>
+      <c r="D107" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="E107" t="s">
-        <v>59</v>
+      <c r="E107" s="1" t="s">
+        <v>52</v>
       </c>
       <c r="F107" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="G107"/>
       <c r="H107"/>
       <c r="I107"/>
       <c r="J107"/>
       <c r="K107" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
     </row>
     <row r="108" ht="25.5" customHeight="1" spans="1:11">
       <c r="A108">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B108" t="s">
-        <v>43</v>
+        <v>117</v>
       </c>
       <c r="C108" t="s">
-        <v>117</v>
-      </c>
-      <c r="D108" t="s">
+        <v>59</v>
+      </c>
+      <c r="D108" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="E108" t="s">
+      <c r="E108" s="1" t="s">
         <v>59</v>
       </c>
       <c r="F108" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G108"/>
       <c r="H108"/>
       <c r="I108"/>
       <c r="J108"/>
       <c r="K108" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
     </row>
     <row r="109" ht="25.5" customHeight="1" spans="1:11">
       <c r="A109">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B109" t="s">
-        <v>43</v>
+        <v>117</v>
       </c>
       <c r="C109" t="s">
-        <v>117</v>
-      </c>
-      <c r="D109" t="s">
+        <v>59</v>
+      </c>
+      <c r="D109" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="E109" t="s">
+      <c r="E109" s="1" t="s">
         <v>59</v>
       </c>
       <c r="F109" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="G109"/>
       <c r="H109"/>
       <c r="I109"/>
       <c r="J109"/>
       <c r="K109" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
     </row>
     <row r="110" ht="25.5" customHeight="1" spans="1:11">
       <c r="A110">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B110" t="s">
-        <v>43</v>
+        <v>117</v>
       </c>
       <c r="C110" t="s">
-        <v>117</v>
-      </c>
-      <c r="D110" t="s">
+        <v>59</v>
+      </c>
+      <c r="D110" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="E110" t="s">
+      <c r="E110" s="1" t="s">
         <v>59</v>
       </c>
       <c r="F110" t="s">
-        <v>147</v>
-      </c>
-      <c r="G110" t="s">
-        <v>147</v>
-      </c>
-      <c r="H110" t="s">
-        <v>147</v>
-      </c>
-      <c r="I110" t="s">
-        <v>147</v>
-      </c>
-      <c r="J110" t="s">
-        <v>147</v>
-      </c>
+        <v>146</v>
+      </c>
+      <c r="G110"/>
+      <c r="H110"/>
+      <c r="I110"/>
+      <c r="J110"/>
       <c r="K110" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
     </row>
     <row r="111" ht="25.5" customHeight="1" spans="1:11">
       <c r="A111">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B111" t="s">
-        <v>43</v>
+        <v>117</v>
       </c>
       <c r="C111" t="s">
-        <v>117</v>
-      </c>
-      <c r="D111" t="s">
+        <v>59</v>
+      </c>
+      <c r="D111" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="E111" t="s">
+      <c r="E111" s="1" t="s">
         <v>59</v>
       </c>
       <c r="F111" t="s">
-        <v>148</v>
-      </c>
-      <c r="G111"/>
-      <c r="H111"/>
-      <c r="I111"/>
-      <c r="J111"/>
+        <v>147</v>
+      </c>
+      <c r="G111" t="s">
+        <v>147</v>
+      </c>
+      <c r="H111" t="s">
+        <v>147</v>
+      </c>
+      <c r="I111" t="s">
+        <v>147</v>
+      </c>
+      <c r="J111" t="s">
+        <v>147</v>
+      </c>
       <c r="K111" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
     </row>
     <row r="112" ht="25.5" customHeight="1" spans="1:11">
       <c r="A112">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B112" t="s">
-        <v>43</v>
+        <v>117</v>
       </c>
       <c r="C112" t="s">
-        <v>117</v>
-      </c>
-      <c r="D112" t="s">
+        <v>59</v>
+      </c>
+      <c r="D112" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="E112" t="s">
-        <v>82</v>
+      <c r="E112" s="1" t="s">
+        <v>59</v>
       </c>
       <c r="F112" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="G112"/>
       <c r="H112"/>
       <c r="I112"/>
       <c r="J112"/>
       <c r="K112" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
     </row>
     <row r="113" ht="25.5" customHeight="1" spans="1:11">
       <c r="A113">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B113" t="s">
-        <v>43</v>
+        <v>117</v>
       </c>
       <c r="C113" t="s">
-        <v>117</v>
-      </c>
-      <c r="D113" t="s">
+        <v>82</v>
+      </c>
+      <c r="D113" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="E113" t="s">
+      <c r="E113" s="1" t="s">
         <v>82</v>
       </c>
       <c r="F113" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="G113"/>
       <c r="H113"/>
       <c r="I113"/>
       <c r="J113"/>
       <c r="K113" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
     </row>
     <row r="114" ht="25.5" customHeight="1" spans="1:11">
       <c r="A114">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B114" t="s">
-        <v>43</v>
+        <v>117</v>
       </c>
       <c r="C114" t="s">
-        <v>117</v>
-      </c>
-      <c r="D114" t="s">
+        <v>82</v>
+      </c>
+      <c r="D114" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="E114" t="s">
+      <c r="E114" s="1" t="s">
         <v>82</v>
       </c>
       <c r="F114" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="G114"/>
       <c r="H114"/>
       <c r="I114"/>
       <c r="J114"/>
       <c r="K114" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
     </row>
     <row r="115" ht="25.5" customHeight="1" spans="1:11">
       <c r="A115">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B115" t="s">
-        <v>43</v>
+        <v>117</v>
       </c>
       <c r="C115" t="s">
-        <v>117</v>
-      </c>
-      <c r="D115" t="s">
+        <v>82</v>
+      </c>
+      <c r="D115" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="E115" t="s">
-        <v>64</v>
+      <c r="E115" s="1" t="s">
+        <v>82</v>
       </c>
       <c r="F115" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="G115"/>
       <c r="H115"/>
       <c r="I115"/>
       <c r="J115"/>
       <c r="K115" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
     </row>
     <row r="116" ht="25.5" customHeight="1" spans="1:11">
       <c r="A116">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B116" t="s">
-        <v>43</v>
+        <v>117</v>
       </c>
       <c r="C116" t="s">
-        <v>117</v>
-      </c>
-      <c r="D116" t="s">
+        <v>64</v>
+      </c>
+      <c r="D116" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="E116" t="s">
+      <c r="E116" s="1" t="s">
         <v>64</v>
       </c>
       <c r="F116" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="G116"/>
       <c r="H116"/>
       <c r="I116"/>
       <c r="J116"/>
       <c r="K116" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
     </row>
     <row r="117" ht="25.5" customHeight="1" spans="1:11">
       <c r="A117">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B117" t="s">
-        <v>43</v>
+        <v>117</v>
       </c>
       <c r="C117" t="s">
-        <v>117</v>
-      </c>
-      <c r="D117" t="s">
+        <v>64</v>
+      </c>
+      <c r="D117" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="E117" t="s">
+      <c r="E117" s="1" t="s">
         <v>64</v>
       </c>
       <c r="F117" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="G117"/>
       <c r="H117"/>
       <c r="I117"/>
       <c r="J117"/>
       <c r="K117" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
     </row>
     <row r="118" ht="25.5" customHeight="1" spans="1:11">
       <c r="A118">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B118" t="s">
-        <v>43</v>
+        <v>117</v>
       </c>
       <c r="C118" t="s">
-        <v>117</v>
-      </c>
-      <c r="D118" t="s">
+        <v>64</v>
+      </c>
+      <c r="D118" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="E118" t="s">
+      <c r="E118" s="1" t="s">
         <v>64</v>
       </c>
       <c r="F118" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="G118"/>
       <c r="H118"/>
       <c r="I118"/>
       <c r="J118"/>
       <c r="K118" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
     </row>
     <row r="119" ht="25.5" customHeight="1" spans="1:11">
       <c r="A119">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B119" t="s">
-        <v>43</v>
+        <v>117</v>
       </c>
       <c r="C119" t="s">
-        <v>117</v>
-      </c>
-      <c r="D119" t="s">
-        <v>93</v>
-      </c>
-      <c r="E119" t="s">
-        <v>94</v>
+        <v>64</v>
+      </c>
+      <c r="D119" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="E119" s="1" t="s">
+        <v>64</v>
       </c>
       <c r="F119" t="s">
-        <v>156</v>
-      </c>
-      <c r="G119" t="s">
-        <v>156</v>
-      </c>
-      <c r="H119" t="s">
-        <v>156</v>
-      </c>
-      <c r="I119" t="s">
-        <v>156</v>
-      </c>
-      <c r="J119" t="s">
-        <v>156</v>
-      </c>
+        <v>155</v>
+      </c>
+      <c r="G119"/>
+      <c r="H119"/>
+      <c r="I119"/>
+      <c r="J119"/>
       <c r="K119" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
     </row>
     <row r="120" ht="25.5" customHeight="1" spans="1:11">
       <c r="A120">
+        <v>112</v>
+      </c>
+      <c r="B120" t="s">
+        <v>117</v>
+      </c>
+      <c r="C120" t="s">
+        <v>93</v>
+      </c>
+      <c r="D120" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="E120" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="F120" t="s">
+        <v>156</v>
+      </c>
+      <c r="G120" t="s">
+        <v>156</v>
+      </c>
+      <c r="H120" t="s">
+        <v>156</v>
+      </c>
+      <c r="I120" t="s">
+        <v>156</v>
+      </c>
+      <c r="J120" t="s">
+        <v>156</v>
+      </c>
+      <c r="K120" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="121" s="1" customFormat="1" ht="25.5" customHeight="1" spans="1:11">
+      <c r="A121" s="1">
         <v>123</v>
       </c>
-      <c r="B120" t="s">
+      <c r="B121" s="1" t="s">
         <v>157</v>
       </c>
-      <c r="C120" t="s">
+      <c r="C121" s="1" t="s">
         <v>158</v>
       </c>
-      <c r="D120" t="s">
+      <c r="D121" s="1" t="s">
         <v>159</v>
       </c>
-      <c r="E120" t="s">
+      <c r="E121" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="F120" t="s">
+      <c r="F121" s="1" t="s">
         <v>159</v>
       </c>
-      <c r="G120" t="s">
+      <c r="G121" s="1" t="s">
         <v>159</v>
       </c>
-      <c r="H120" t="s">
+      <c r="H121" s="1" t="s">
         <v>159</v>
       </c>
-      <c r="I120" t="s">
+      <c r="I121" s="1" t="s">
         <v>159</v>
       </c>
-      <c r="J120" t="s">
+      <c r="J121" s="1" t="s">
         <v>159</v>
       </c>
-      <c r="K120" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="121" ht="25.5" customHeight="1" spans="1:11">
-      <c r="A121">
-        <v>124</v>
-      </c>
-      <c r="B121" t="s">
-        <v>157</v>
-      </c>
-      <c r="C121" t="s">
-        <v>160</v>
-      </c>
-      <c r="D121" t="s">
-        <v>161</v>
-      </c>
-      <c r="E121" t="s">
-        <v>162</v>
-      </c>
-      <c r="F121" t="s">
-        <v>163</v>
-      </c>
-      <c r="G121" t="s">
-        <v>163</v>
-      </c>
-      <c r="H121" t="s">
-        <v>163</v>
-      </c>
-      <c r="I121" t="s">
-        <v>163</v>
-      </c>
-      <c r="J121" t="s">
-        <v>163</v>
-      </c>
-      <c r="K121" t="s">
-        <v>14</v>
+      <c r="K121" s="1" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="122" ht="25.5" customHeight="1" spans="1:11">
       <c r="A122">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B122" t="s">
         <v>157</v>
@@ -5447,34 +5408,34 @@
       <c r="C122" t="s">
         <v>160</v>
       </c>
-      <c r="D122" t="s">
+      <c r="D122" s="1" t="s">
         <v>161</v>
       </c>
-      <c r="E122" t="s">
+      <c r="E122" s="1" t="s">
         <v>162</v>
       </c>
       <c r="F122" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="G122" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="H122" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="I122" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="J122" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="K122" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
     </row>
     <row r="123" ht="25.5" customHeight="1" spans="1:11">
       <c r="A123">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B123" t="s">
         <v>157</v>
@@ -5482,34 +5443,34 @@
       <c r="C123" t="s">
         <v>160</v>
       </c>
-      <c r="D123" t="s">
+      <c r="D123" s="1" t="s">
         <v>161</v>
       </c>
-      <c r="E123" t="s">
+      <c r="E123" s="1" t="s">
         <v>162</v>
       </c>
       <c r="F123" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="G123" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="H123" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="I123" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="J123" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="K123" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
     </row>
     <row r="124" ht="25.5" customHeight="1" spans="1:11">
       <c r="A124">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B124" t="s">
         <v>157</v>
@@ -5517,34 +5478,34 @@
       <c r="C124" t="s">
         <v>160</v>
       </c>
-      <c r="D124" t="s">
+      <c r="D124" s="1" t="s">
         <v>161</v>
       </c>
-      <c r="E124" t="s">
+      <c r="E124" s="1" t="s">
         <v>162</v>
       </c>
       <c r="F124" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="G124" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="H124" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="I124" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="J124" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="K124" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
     </row>
     <row r="125" ht="25.5" customHeight="1" spans="1:11">
       <c r="A125">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B125" t="s">
         <v>157</v>
@@ -5552,34 +5513,34 @@
       <c r="C125" t="s">
         <v>160</v>
       </c>
-      <c r="D125" t="s">
+      <c r="D125" s="1" t="s">
         <v>161</v>
       </c>
-      <c r="E125" t="s">
+      <c r="E125" s="1" t="s">
         <v>162</v>
       </c>
       <c r="F125" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="G125" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="H125" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="I125" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="J125" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="K125" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
     </row>
     <row r="126" ht="25.5" customHeight="1" spans="1:11">
       <c r="A126">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B126" t="s">
         <v>157</v>
@@ -5587,34 +5548,34 @@
       <c r="C126" t="s">
         <v>160</v>
       </c>
-      <c r="D126" t="s">
+      <c r="D126" s="1" t="s">
         <v>161</v>
       </c>
-      <c r="E126" t="s">
+      <c r="E126" s="1" t="s">
         <v>162</v>
       </c>
       <c r="F126" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="G126" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="H126" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="I126" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="J126" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="K126" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
     </row>
     <row r="127" ht="25.5" customHeight="1" spans="1:11">
       <c r="A127">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B127" t="s">
         <v>157</v>
@@ -5622,34 +5583,34 @@
       <c r="C127" t="s">
         <v>160</v>
       </c>
-      <c r="D127" t="s">
+      <c r="D127" s="1" t="s">
         <v>161</v>
       </c>
-      <c r="E127" t="s">
+      <c r="E127" s="1" t="s">
         <v>162</v>
       </c>
       <c r="F127" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="G127" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="H127" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="I127" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="J127" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="K127" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
     </row>
     <row r="128" ht="25.5" customHeight="1" spans="1:11">
       <c r="A128">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B128" t="s">
         <v>157</v>
@@ -5657,34 +5618,34 @@
       <c r="C128" t="s">
         <v>160</v>
       </c>
-      <c r="D128" t="s">
+      <c r="D128" s="1" t="s">
         <v>161</v>
       </c>
-      <c r="E128" t="s">
+      <c r="E128" s="1" t="s">
         <v>162</v>
       </c>
       <c r="F128" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="G128" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="H128" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="I128" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="J128" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="K128" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
     </row>
     <row r="129" ht="25.5" customHeight="1" spans="1:11">
       <c r="A129">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B129" t="s">
         <v>157</v>
@@ -5692,26 +5653,34 @@
       <c r="C129" t="s">
         <v>160</v>
       </c>
-      <c r="D129" t="s">
-        <v>171</v>
-      </c>
-      <c r="E129" t="s">
+      <c r="D129" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="E129" s="1" t="s">
         <v>162</v>
       </c>
       <c r="F129" t="s">
-        <v>172</v>
-      </c>
-      <c r="G129"/>
-      <c r="H129"/>
-      <c r="I129"/>
-      <c r="J129"/>
+        <v>170</v>
+      </c>
+      <c r="G129" t="s">
+        <v>170</v>
+      </c>
+      <c r="H129" t="s">
+        <v>170</v>
+      </c>
+      <c r="I129" t="s">
+        <v>170</v>
+      </c>
+      <c r="J129" t="s">
+        <v>170</v>
+      </c>
       <c r="K129" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
     </row>
     <row r="130" ht="25.5" customHeight="1" spans="1:11">
       <c r="A130">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B130" t="s">
         <v>157</v>
@@ -5719,34 +5688,26 @@
       <c r="C130" t="s">
         <v>160</v>
       </c>
-      <c r="D130" t="s">
+      <c r="D130" s="1" t="s">
         <v>171</v>
       </c>
-      <c r="E130" t="s">
+      <c r="E130" s="1" t="s">
         <v>162</v>
       </c>
       <c r="F130" t="s">
-        <v>173</v>
-      </c>
-      <c r="G130" t="s">
-        <v>173</v>
-      </c>
-      <c r="H130" t="s">
-        <v>173</v>
-      </c>
-      <c r="I130" t="s">
-        <v>173</v>
-      </c>
-      <c r="J130" t="s">
-        <v>173</v>
-      </c>
+        <v>172</v>
+      </c>
+      <c r="G130"/>
+      <c r="H130"/>
+      <c r="I130"/>
+      <c r="J130"/>
       <c r="K130" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
     </row>
     <row r="131" ht="25.5" customHeight="1" spans="1:11">
       <c r="A131">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B131" t="s">
         <v>157</v>
@@ -5754,34 +5715,34 @@
       <c r="C131" t="s">
         <v>160</v>
       </c>
-      <c r="D131" t="s">
+      <c r="D131" s="1" t="s">
         <v>171</v>
       </c>
-      <c r="E131" t="s">
+      <c r="E131" s="1" t="s">
         <v>162</v>
       </c>
       <c r="F131" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="G131" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="H131" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="I131" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="J131" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="K131" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
     </row>
     <row r="132" ht="25.5" customHeight="1" spans="1:11">
       <c r="A132">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B132" t="s">
         <v>157</v>
@@ -5789,34 +5750,34 @@
       <c r="C132" t="s">
         <v>160</v>
       </c>
-      <c r="D132" t="s">
+      <c r="D132" s="1" t="s">
         <v>171</v>
       </c>
-      <c r="E132" t="s">
+      <c r="E132" s="1" t="s">
         <v>162</v>
       </c>
       <c r="F132" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="G132" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="H132" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="I132" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="J132" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="K132" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
     </row>
     <row r="133" ht="25.5" customHeight="1" spans="1:11">
       <c r="A133">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B133" t="s">
         <v>157</v>
@@ -5824,34 +5785,34 @@
       <c r="C133" t="s">
         <v>160</v>
       </c>
-      <c r="D133" t="s">
+      <c r="D133" s="1" t="s">
         <v>171</v>
       </c>
-      <c r="E133" t="s">
+      <c r="E133" s="1" t="s">
         <v>162</v>
       </c>
       <c r="F133" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="G133" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="H133" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="I133" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="J133" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="K133" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
     </row>
     <row r="134" ht="25.5" customHeight="1" spans="1:11">
       <c r="A134">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="B134" t="s">
         <v>157</v>
@@ -5859,34 +5820,34 @@
       <c r="C134" t="s">
         <v>160</v>
       </c>
-      <c r="D134" t="s">
+      <c r="D134" s="1" t="s">
         <v>171</v>
       </c>
-      <c r="E134" t="s">
+      <c r="E134" s="1" t="s">
         <v>162</v>
       </c>
       <c r="F134" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="G134" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="H134" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="I134" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="J134" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="K134" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
     </row>
     <row r="135" ht="25.5" customHeight="1" spans="1:11">
       <c r="A135">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B135" t="s">
         <v>157</v>
@@ -5894,34 +5855,34 @@
       <c r="C135" t="s">
         <v>160</v>
       </c>
-      <c r="D135" t="s">
+      <c r="D135" s="1" t="s">
         <v>171</v>
       </c>
-      <c r="E135" t="s">
+      <c r="E135" s="1" t="s">
         <v>162</v>
       </c>
       <c r="F135" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="G135" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="H135" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="I135" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="J135" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="K135" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
     </row>
     <row r="136" ht="25.5" customHeight="1" spans="1:11">
       <c r="A136">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B136" t="s">
         <v>157</v>
@@ -5929,26 +5890,34 @@
       <c r="C136" t="s">
         <v>160</v>
       </c>
-      <c r="D136" t="s">
+      <c r="D136" s="1" t="s">
         <v>171</v>
       </c>
-      <c r="E136" t="s">
+      <c r="E136" s="1" t="s">
         <v>162</v>
       </c>
       <c r="F136" t="s">
-        <v>179</v>
-      </c>
-      <c r="G136"/>
-      <c r="H136"/>
-      <c r="I136"/>
-      <c r="J136"/>
+        <v>178</v>
+      </c>
+      <c r="G136" t="s">
+        <v>178</v>
+      </c>
+      <c r="H136" t="s">
+        <v>178</v>
+      </c>
+      <c r="I136" t="s">
+        <v>178</v>
+      </c>
+      <c r="J136" t="s">
+        <v>178</v>
+      </c>
       <c r="K136" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
     </row>
     <row r="137" ht="25.5" customHeight="1" spans="1:11">
       <c r="A137">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="B137" t="s">
         <v>157</v>
@@ -5956,69 +5925,61 @@
       <c r="C137" t="s">
         <v>160</v>
       </c>
-      <c r="D137" t="s">
+      <c r="D137" s="1" t="s">
         <v>171</v>
       </c>
-      <c r="E137" t="s">
+      <c r="E137" s="1" t="s">
         <v>162</v>
       </c>
       <c r="F137" t="s">
-        <v>180</v>
-      </c>
-      <c r="G137" t="s">
-        <v>180</v>
-      </c>
-      <c r="H137" t="s">
-        <v>180</v>
-      </c>
-      <c r="I137" t="s">
-        <v>180</v>
-      </c>
-      <c r="J137" t="s">
-        <v>180</v>
-      </c>
+        <v>179</v>
+      </c>
+      <c r="G137"/>
+      <c r="H137"/>
+      <c r="I137"/>
+      <c r="J137"/>
       <c r="K137" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
     </row>
     <row r="138" ht="25.5" customHeight="1" spans="1:11">
       <c r="A138">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="B138" t="s">
         <v>157</v>
       </c>
       <c r="C138" t="s">
-        <v>181</v>
-      </c>
-      <c r="D138" t="s">
-        <v>182</v>
-      </c>
-      <c r="E138" t="s">
-        <v>183</v>
+        <v>160</v>
+      </c>
+      <c r="D138" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="E138" s="1" t="s">
+        <v>162</v>
       </c>
       <c r="F138" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="G138" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="H138" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="I138" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="J138" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="K138" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
     </row>
     <row r="139" ht="25.5" customHeight="1" spans="1:11">
       <c r="A139">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B139" t="s">
         <v>157</v>
@@ -6026,34 +5987,34 @@
       <c r="C139" t="s">
         <v>181</v>
       </c>
-      <c r="D139" t="s">
+      <c r="D139" s="1" t="s">
         <v>182</v>
       </c>
-      <c r="E139" t="s">
+      <c r="E139" s="1" t="s">
         <v>183</v>
       </c>
       <c r="F139" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="G139" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="H139" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="I139" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="J139" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="K139" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
     </row>
     <row r="140" ht="25.5" customHeight="1" spans="1:11">
       <c r="A140">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B140" t="s">
         <v>157</v>
@@ -6061,26 +6022,34 @@
       <c r="C140" t="s">
         <v>181</v>
       </c>
-      <c r="D140" t="s">
+      <c r="D140" s="1" t="s">
         <v>182</v>
       </c>
-      <c r="E140" t="s">
+      <c r="E140" s="1" t="s">
         <v>183</v>
       </c>
       <c r="F140" t="s">
-        <v>186</v>
-      </c>
-      <c r="G140"/>
-      <c r="H140"/>
-      <c r="I140"/>
-      <c r="J140"/>
+        <v>185</v>
+      </c>
+      <c r="G140" t="s">
+        <v>185</v>
+      </c>
+      <c r="H140" t="s">
+        <v>185</v>
+      </c>
+      <c r="I140" t="s">
+        <v>185</v>
+      </c>
+      <c r="J140" t="s">
+        <v>185</v>
+      </c>
       <c r="K140" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
     </row>
     <row r="141" ht="25.5" customHeight="1" spans="1:11">
       <c r="A141">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="B141" t="s">
         <v>157</v>
@@ -6088,34 +6057,26 @@
       <c r="C141" t="s">
         <v>181</v>
       </c>
-      <c r="D141" t="s">
+      <c r="D141" s="1" t="s">
         <v>182</v>
       </c>
-      <c r="E141" t="s">
+      <c r="E141" s="1" t="s">
         <v>183</v>
       </c>
       <c r="F141" t="s">
-        <v>187</v>
-      </c>
-      <c r="G141" t="s">
-        <v>187</v>
-      </c>
-      <c r="H141" t="s">
-        <v>187</v>
-      </c>
-      <c r="I141" t="s">
-        <v>187</v>
-      </c>
-      <c r="J141" t="s">
-        <v>187</v>
-      </c>
+        <v>186</v>
+      </c>
+      <c r="G141"/>
+      <c r="H141"/>
+      <c r="I141"/>
+      <c r="J141"/>
       <c r="K141" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
     </row>
     <row r="142" ht="25.5" customHeight="1" spans="1:11">
       <c r="A142">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="B142" t="s">
         <v>157</v>
@@ -6123,34 +6084,34 @@
       <c r="C142" t="s">
         <v>181</v>
       </c>
-      <c r="D142" t="s">
+      <c r="D142" s="1" t="s">
         <v>182</v>
       </c>
-      <c r="E142" t="s">
+      <c r="E142" s="1" t="s">
         <v>183</v>
       </c>
       <c r="F142" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="G142" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="H142" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="I142" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="J142" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="K142" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
     </row>
     <row r="143" ht="25.5" customHeight="1" spans="1:11">
       <c r="A143">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="B143" t="s">
         <v>157</v>
@@ -6158,425 +6119,400 @@
       <c r="C143" t="s">
         <v>181</v>
       </c>
-      <c r="D143" t="s">
+      <c r="D143" s="1" t="s">
         <v>182</v>
       </c>
-      <c r="E143" t="s">
+      <c r="E143" s="1" t="s">
         <v>183</v>
       </c>
       <c r="F143" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="G143" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="H143" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="I143" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="J143" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="K143" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
     </row>
     <row r="144" ht="25.5" customHeight="1" spans="1:11">
       <c r="A144">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="B144" t="s">
         <v>157</v>
       </c>
       <c r="C144" t="s">
-        <v>190</v>
-      </c>
-      <c r="D144" t="s">
-        <v>190</v>
-      </c>
-      <c r="E144" t="s">
-        <v>191</v>
+        <v>181</v>
+      </c>
+      <c r="D144" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="E144" s="1" t="s">
+        <v>183</v>
       </c>
       <c r="F144" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="G144" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="H144" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="I144" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="J144" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="K144" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
     </row>
     <row r="145" ht="25.5" customHeight="1" spans="1:11">
       <c r="A145">
-        <v>113</v>
+        <v>147</v>
       </c>
       <c r="B145" t="s">
-        <v>192</v>
+        <v>157</v>
       </c>
       <c r="C145" t="s">
-        <v>192</v>
-      </c>
-      <c r="D145" t="s">
-        <v>193</v>
-      </c>
-      <c r="E145" t="s">
-        <v>32</v>
+        <v>190</v>
+      </c>
+      <c r="D145" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="E145" s="1" t="s">
+        <v>191</v>
       </c>
       <c r="F145" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="G145" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="H145" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="I145" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="J145" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="K145" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
     </row>
     <row r="146" ht="25.5" customHeight="1" spans="1:11">
       <c r="A146">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B146" t="s">
         <v>192</v>
       </c>
-      <c r="C146" t="s">
-        <v>192</v>
-      </c>
-      <c r="D146" t="s">
-        <v>194</v>
-      </c>
-      <c r="E146" t="s">
-        <v>32</v>
-      </c>
+      <c r="C146"/>
+      <c r="D146" s="1"/>
+      <c r="E146" s="1"/>
       <c r="F146" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="G146" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="H146" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="I146" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="J146" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="K146" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
     </row>
     <row r="147" ht="25.5" customHeight="1" spans="1:11">
       <c r="A147">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B147" t="s">
         <v>192</v>
       </c>
-      <c r="C147" t="s">
-        <v>192</v>
-      </c>
-      <c r="D147" t="s">
-        <v>195</v>
-      </c>
-      <c r="E147" t="s">
-        <v>32</v>
-      </c>
+      <c r="C147"/>
+      <c r="D147" s="1"/>
+      <c r="E147" s="1"/>
       <c r="F147" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="G147" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="H147" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="I147" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="J147" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="K147" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
     </row>
     <row r="148" ht="25.5" customHeight="1" spans="1:11">
       <c r="A148">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B148" t="s">
         <v>192</v>
       </c>
-      <c r="C148" t="s">
-        <v>192</v>
-      </c>
-      <c r="D148" t="s">
-        <v>196</v>
-      </c>
-      <c r="E148" t="s">
-        <v>32</v>
-      </c>
+      <c r="C148"/>
+      <c r="D148" s="1"/>
+      <c r="E148" s="1"/>
       <c r="F148" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="G148" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="H148" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="I148" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="J148" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="K148" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
     </row>
     <row r="149" ht="25.5" customHeight="1" spans="1:11">
       <c r="A149">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B149" t="s">
         <v>192</v>
       </c>
-      <c r="C149" t="s">
-        <v>192</v>
-      </c>
-      <c r="D149" t="s">
-        <v>197</v>
-      </c>
-      <c r="E149" t="s">
-        <v>32</v>
-      </c>
+      <c r="C149"/>
+      <c r="D149" s="1"/>
+      <c r="E149" s="1"/>
       <c r="F149" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="G149" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="H149" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="I149" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="J149" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="K149" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
     </row>
     <row r="150" ht="25.5" customHeight="1" spans="1:11">
       <c r="A150">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B150" t="s">
         <v>192</v>
       </c>
-      <c r="C150" t="s">
-        <v>192</v>
-      </c>
-      <c r="D150" t="s">
-        <v>198</v>
-      </c>
-      <c r="E150" t="s">
-        <v>32</v>
-      </c>
+      <c r="C150"/>
+      <c r="D150" s="1"/>
+      <c r="E150" s="1"/>
       <c r="F150" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="G150" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="H150" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="I150" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="J150" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="K150" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
     </row>
     <row r="151" ht="25.5" customHeight="1" spans="1:11">
       <c r="A151">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B151" t="s">
-        <v>158</v>
-      </c>
-      <c r="C151" t="s">
-        <v>158</v>
-      </c>
-      <c r="D151" t="s">
-        <v>199</v>
-      </c>
-      <c r="E151" t="s">
-        <v>32</v>
-      </c>
+        <v>192</v>
+      </c>
+      <c r="C151"/>
+      <c r="D151" s="1"/>
+      <c r="E151" s="1"/>
       <c r="F151" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="G151" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="H151" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="I151" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="J151" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="K151" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
     </row>
     <row r="152" ht="25.5" customHeight="1" spans="1:11">
       <c r="A152">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B152" t="s">
         <v>158</v>
       </c>
-      <c r="C152" t="s">
-        <v>158</v>
-      </c>
-      <c r="D152" t="s">
-        <v>200</v>
-      </c>
-      <c r="E152" t="s">
-        <v>32</v>
-      </c>
+      <c r="C152"/>
+      <c r="D152" s="1"/>
+      <c r="E152" s="1"/>
       <c r="F152" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="G152" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="H152" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="I152" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="J152" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="K152" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
     </row>
     <row r="153" ht="25.5" customHeight="1" spans="1:11">
       <c r="A153">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B153" t="s">
         <v>158</v>
       </c>
-      <c r="C153" t="s">
-        <v>158</v>
-      </c>
-      <c r="D153" t="s">
-        <v>201</v>
-      </c>
-      <c r="E153" t="s">
-        <v>32</v>
-      </c>
+      <c r="C153"/>
+      <c r="D153" s="1"/>
+      <c r="E153" s="1"/>
       <c r="F153" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="G153" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="H153" t="s">
-        <v>201</v>
-      </c>
-      <c r="I153"/>
-      <c r="J153"/>
+        <v>200</v>
+      </c>
+      <c r="I153" t="s">
+        <v>200</v>
+      </c>
+      <c r="J153" t="s">
+        <v>200</v>
+      </c>
       <c r="K153" t="s">
-        <v>73</v>
+        <v>17</v>
       </c>
     </row>
     <row r="154" ht="25.5" customHeight="1" spans="1:11">
       <c r="A154">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="B154" t="s">
         <v>158</v>
       </c>
-      <c r="C154" t="s">
+      <c r="C154"/>
+      <c r="D154" s="1"/>
+      <c r="E154" s="1"/>
+      <c r="F154" t="s">
+        <v>201</v>
+      </c>
+      <c r="G154" t="s">
+        <v>201</v>
+      </c>
+      <c r="H154" t="s">
+        <v>201</v>
+      </c>
+      <c r="I154"/>
+      <c r="J154"/>
+      <c r="K154" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="155" ht="25.5" customHeight="1" spans="1:11">
+      <c r="A155">
+        <v>122</v>
+      </c>
+      <c r="B155" t="s">
         <v>158</v>
       </c>
-      <c r="D154" t="s">
+      <c r="C155"/>
+      <c r="D155" s="1"/>
+      <c r="E155" s="1"/>
+      <c r="F155" t="s">
         <v>202</v>
       </c>
-      <c r="E154" t="s">
-        <v>32</v>
-      </c>
-      <c r="F154" t="s">
+      <c r="G155" t="s">
         <v>202</v>
       </c>
-      <c r="G154" t="s">
+      <c r="H155" t="s">
         <v>202</v>
       </c>
-      <c r="H154" t="s">
+      <c r="I155" t="s">
         <v>202</v>
       </c>
-      <c r="I154" t="s">
+      <c r="J155" t="s">
         <v>202</v>
       </c>
-      <c r="J154" t="s">
-        <v>202</v>
-      </c>
-      <c r="K154" t="s">
-        <v>14</v>
+      <c r="K155" t="s">
+        <v>17</v>
       </c>
     </row>
   </sheetData>
   <dataValidations count="4">
-    <dataValidation type="list" sqref="B2:B153">
+    <dataValidation type="list" sqref="B3:B20 B121:B154">
       <formula1>"后勤管理中心,三大区域,商业业务,科创发展中心,战略支持中心,后勤集团总裁室"</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="C2:C153">
+    <dataValidation type="list" sqref="B21:B120 C3:C20 C121:C154">
       <formula1>"教育园特色餐饮,念心湖酒店,海亮后勤车队,海亮医院,中心其余业务部门,中心管理部门,西南区域,东部区域,北部区域,战略支持中心,商超业务-便利店,商超业务-商业街,科创发展中心,线下商超-便利店,线上商城业务,后勤集团总裁室,线下商超-商业街,融爱星餐饮"</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="D2:D153">
+    <dataValidation type="list" sqref="C21:C120 E3:E154">
+      <formula1>"区域配送业务,区域餐饮业务,区域商超业务,区域物业业务,区域科技业务,区域总经理室,线下便利店,线上商城,中心餐饮业务,中心物业业务,其他,管理部门,线下商业街"</formula1>
+    </dataValidation>
+    <dataValidation type="list" sqref="D3:D154">
       <formula1>"科研大厦食堂,存量,增量,两校一园便利店,海亮医院,教育园特色餐饮,后勤综合管理部,区域管理部门,异地便利店,后勤商业街,后勤数智零售部,后勤一卡通管理,后勤餐饮运营部,湘湖后勤,后勤解决方案部,后勤市场管理部,后勤学院,后勤财务管理部,后勤品牌战略部,后勤安全管理部,海亮后勤车队,酒店本级,后勤人资管理部,托管学校入模产品服务,后勤数智研发部,后勤集团总裁室,后勤加工中心,后勤物业管理部,后勤管理中心总监室,线上商城业务,后勤供应发展部,教育园店,社会店"</formula1>
-    </dataValidation>
-    <dataValidation type="list" sqref="E2:E153">
-      <formula1>"区域配送业务,区域餐饮业务,区域商超业务,区域物业业务,区域科技业务,区域总经理室,线下便利店,线上商城,中心餐饮业务,中心物业业务,其他,管理部门,线下商业街"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/docs/data/教育后勤2025经营数据看版_组织标签映射表-勿动.xlsx
+++ b/docs/data/教育后勤2025经营数据看版_组织标签映射表-勿动.xlsx
@@ -10,7 +10,7 @@
     <sheet name="组织标签映射表-勿动" sheetId="2" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'组织标签映射表-勿动'!$A$6:$E$158</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'组织标签映射表-勿动'!$A$1:$D$159</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="608" uniqueCount="180">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="629" uniqueCount="186">
   <si>
     <t>level_0</t>
   </si>
@@ -359,7 +359,10 @@
     <t>玉门一中后勤</t>
   </si>
   <si>
-    <t>周口示范区物业</t>
+    <t>周口示范区物业项目</t>
+  </si>
+  <si>
+    <t>修改</t>
   </si>
   <si>
     <t>安全管理平台</t>
@@ -570,6 +573,21 @@
   </si>
   <si>
     <t>后勤数智研发部</t>
+  </si>
+  <si>
+    <t>虎林配送</t>
+  </si>
+  <si>
+    <t>新增</t>
+  </si>
+  <si>
+    <t>亳州地区福利外拓</t>
+  </si>
+  <si>
+    <t>镇沅一中食堂</t>
+  </si>
+  <si>
+    <t>长顺项目本级</t>
   </si>
 </sst>
 </file>
@@ -582,7 +600,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="23">
+  <fonts count="26">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -598,6 +616,24 @@
       <sz val="10"/>
       <name val="Calibri"/>
       <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="DengXian"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="微软雅黑"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
@@ -951,12 +987,27 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="9">
+  <borders count="10">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -1060,31 +1111,19 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1093,119 +1132,131 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
@@ -1213,6 +1264,13 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1280,6 +1338,11 @@
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <mruColors>
+      <color rgb="00FF0000"/>
+    </mruColors>
+  </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -1546,8 +1609,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D155"/>
-  <sheetFormatPr defaultColWidth="10" defaultRowHeight="13.8" outlineLevelCol="3"/>
+  <dimension ref="A1:F159"/>
+  <sheetFormatPr defaultColWidth="10" defaultRowHeight="13.8" outlineLevelCol="5"/>
   <cols>
     <col min="1" max="2" width="19" customWidth="1"/>
     <col min="3" max="3" width="17.2222222222222" customWidth="1"/>
@@ -2808,7 +2871,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="91" ht="25.5" customHeight="1" spans="1:4">
+    <row r="91" ht="25.5" customHeight="1" spans="1:6">
       <c r="A91" t="s">
         <v>4</v>
       </c>
@@ -2818,8 +2881,14 @@
       <c r="C91" t="s">
         <v>64</v>
       </c>
-      <c r="D91" t="s">
+      <c r="D91" s="5" t="s">
         <v>109</v>
+      </c>
+      <c r="E91" t="s">
+        <v>110</v>
+      </c>
+      <c r="F91">
+        <v>20260407</v>
       </c>
     </row>
     <row r="92" ht="25.5" customHeight="1" spans="1:4">
@@ -2833,7 +2902,7 @@
         <v>48</v>
       </c>
       <c r="D92" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
     </row>
     <row r="93" ht="25.5" customHeight="1" spans="1:4">
@@ -2847,7 +2916,7 @@
         <v>30</v>
       </c>
       <c r="D93" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
     </row>
     <row r="94" ht="25.5" customHeight="1" spans="1:4">
@@ -2861,7 +2930,7 @@
         <v>30</v>
       </c>
       <c r="D94" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
     </row>
     <row r="95" ht="25.5" customHeight="1" spans="1:4">
@@ -2875,7 +2944,7 @@
         <v>30</v>
       </c>
       <c r="D95" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
     <row r="96" ht="25.5" customHeight="1" spans="1:4">
@@ -2889,7 +2958,7 @@
         <v>30</v>
       </c>
       <c r="D96" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
     <row r="97" ht="25.5" customHeight="1" spans="1:4">
@@ -2903,7 +2972,7 @@
         <v>30</v>
       </c>
       <c r="D97" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
     </row>
     <row r="98" ht="25.5" customHeight="1" spans="1:4">
@@ -2917,7 +2986,7 @@
         <v>30</v>
       </c>
       <c r="D98" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="99" ht="25.5" customHeight="1" spans="1:4">
@@ -2931,7 +3000,7 @@
         <v>36</v>
       </c>
       <c r="D99" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
     </row>
     <row r="100" ht="25.5" customHeight="1" spans="1:4">
@@ -2945,7 +3014,7 @@
         <v>36</v>
       </c>
       <c r="D100" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="101" ht="25.5" customHeight="1" spans="1:4">
@@ -2959,7 +3028,7 @@
         <v>36</v>
       </c>
       <c r="D101" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="102" ht="25.5" customHeight="1" spans="1:4">
@@ -2973,7 +3042,7 @@
         <v>36</v>
       </c>
       <c r="D102" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="103" ht="25.5" customHeight="1" spans="1:4">
@@ -2987,7 +3056,7 @@
         <v>36</v>
       </c>
       <c r="D103" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="104" ht="25.5" customHeight="1" spans="1:4">
@@ -3001,7 +3070,7 @@
         <v>36</v>
       </c>
       <c r="D104" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="105" ht="25.5" customHeight="1" spans="1:4">
@@ -3015,7 +3084,7 @@
         <v>36</v>
       </c>
       <c r="D105" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
     </row>
     <row r="106" ht="25.5" customHeight="1" spans="1:4">
@@ -3029,7 +3098,7 @@
         <v>36</v>
       </c>
       <c r="D106" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
     </row>
     <row r="107" ht="25.5" customHeight="1" spans="1:4">
@@ -3043,7 +3112,7 @@
         <v>36</v>
       </c>
       <c r="D107" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
     </row>
     <row r="108" ht="25.5" customHeight="1" spans="1:4">
@@ -3057,7 +3126,7 @@
         <v>43</v>
       </c>
       <c r="D108" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
     </row>
     <row r="109" ht="25.5" customHeight="1" spans="1:4">
@@ -3071,7 +3140,7 @@
         <v>43</v>
       </c>
       <c r="D109" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="110" ht="25.5" customHeight="1" spans="1:4">
@@ -3085,7 +3154,7 @@
         <v>43</v>
       </c>
       <c r="D110" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
     </row>
     <row r="111" ht="25.5" customHeight="1" spans="1:4">
@@ -3099,7 +3168,7 @@
         <v>43</v>
       </c>
       <c r="D111" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
     </row>
     <row r="112" ht="25.5" customHeight="1" spans="1:4">
@@ -3113,7 +3182,7 @@
         <v>43</v>
       </c>
       <c r="D112" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
     </row>
     <row r="113" ht="25.5" customHeight="1" spans="1:4">
@@ -3127,7 +3196,7 @@
         <v>64</v>
       </c>
       <c r="D113" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
     </row>
     <row r="114" ht="25.5" customHeight="1" spans="1:4">
@@ -3141,7 +3210,7 @@
         <v>64</v>
       </c>
       <c r="D114" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
     </row>
     <row r="115" ht="25.5" customHeight="1" spans="1:4">
@@ -3155,7 +3224,7 @@
         <v>64</v>
       </c>
       <c r="D115" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
     </row>
     <row r="116" ht="25.5" customHeight="1" spans="1:4">
@@ -3169,7 +3238,7 @@
         <v>48</v>
       </c>
       <c r="D116" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
     </row>
     <row r="117" ht="25.5" customHeight="1" spans="1:4">
@@ -3183,7 +3252,7 @@
         <v>48</v>
       </c>
       <c r="D117" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="118" ht="25.5" customHeight="1" spans="1:4">
@@ -3197,7 +3266,7 @@
         <v>48</v>
       </c>
       <c r="D118" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
     </row>
     <row r="119" ht="25.5" customHeight="1" spans="1:4">
@@ -3211,7 +3280,7 @@
         <v>48</v>
       </c>
       <c r="D119" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
     </row>
     <row r="120" ht="25.5" customHeight="1" spans="1:4">
@@ -3225,7 +3294,7 @@
         <v>75</v>
       </c>
       <c r="D120" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
     </row>
     <row r="121" s="2" customFormat="1" ht="25.5" customHeight="1" spans="1:4">
@@ -3233,13 +3302,13 @@
         <v>4</v>
       </c>
       <c r="B121" s="2" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C121" s="2" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="D121" s="2" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
     </row>
     <row r="122" ht="25.5" customHeight="1" spans="1:4">
@@ -3247,13 +3316,13 @@
         <v>4</v>
       </c>
       <c r="B122" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C122" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="D122" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
     </row>
     <row r="123" ht="25.5" customHeight="1" spans="1:4">
@@ -3261,13 +3330,13 @@
         <v>4</v>
       </c>
       <c r="B123" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C123" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="D123" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
     </row>
     <row r="124" ht="25.5" customHeight="1" spans="1:4">
@@ -3275,13 +3344,13 @@
         <v>4</v>
       </c>
       <c r="B124" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C124" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="D124" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="125" ht="25.5" customHeight="1" spans="1:4">
@@ -3289,13 +3358,13 @@
         <v>4</v>
       </c>
       <c r="B125" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C125" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="D125" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
     </row>
     <row r="126" ht="25.5" customHeight="1" spans="1:4">
@@ -3303,13 +3372,13 @@
         <v>4</v>
       </c>
       <c r="B126" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C126" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="D126" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
     </row>
     <row r="127" ht="25.5" customHeight="1" spans="1:4">
@@ -3317,13 +3386,13 @@
         <v>4</v>
       </c>
       <c r="B127" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C127" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="D127" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
     </row>
     <row r="128" ht="25.5" customHeight="1" spans="1:4">
@@ -3331,13 +3400,13 @@
         <v>4</v>
       </c>
       <c r="B128" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C128" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="D128" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
     </row>
     <row r="129" ht="25.5" customHeight="1" spans="1:4">
@@ -3345,13 +3414,13 @@
         <v>4</v>
       </c>
       <c r="B129" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C129" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="D129" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
     </row>
     <row r="130" ht="25.5" customHeight="1" spans="1:4">
@@ -3359,13 +3428,13 @@
         <v>4</v>
       </c>
       <c r="B130" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C130" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="D130" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
     </row>
     <row r="131" ht="25.5" customHeight="1" spans="1:4">
@@ -3373,13 +3442,13 @@
         <v>4</v>
       </c>
       <c r="B131" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C131" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="D131" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
     </row>
     <row r="132" ht="25.5" customHeight="1" spans="1:4">
@@ -3387,13 +3456,13 @@
         <v>4</v>
       </c>
       <c r="B132" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C132" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="D132" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
     </row>
     <row r="133" ht="25.5" customHeight="1" spans="1:4">
@@ -3401,13 +3470,13 @@
         <v>4</v>
       </c>
       <c r="B133" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C133" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="D133" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
     </row>
     <row r="134" ht="25.5" customHeight="1" spans="1:4">
@@ -3415,13 +3484,13 @@
         <v>4</v>
       </c>
       <c r="B134" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C134" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="D134" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
     </row>
     <row r="135" ht="25.5" customHeight="1" spans="1:4">
@@ -3429,13 +3498,13 @@
         <v>4</v>
       </c>
       <c r="B135" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C135" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="D135" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
     </row>
     <row r="136" ht="25.5" customHeight="1" spans="1:4">
@@ -3443,13 +3512,13 @@
         <v>4</v>
       </c>
       <c r="B136" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C136" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="D136" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
     </row>
     <row r="137" ht="25.5" customHeight="1" spans="1:4">
@@ -3457,13 +3526,13 @@
         <v>4</v>
       </c>
       <c r="B137" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C137" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="D137" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
     </row>
     <row r="138" ht="25.5" customHeight="1" spans="1:4">
@@ -3471,13 +3540,13 @@
         <v>4</v>
       </c>
       <c r="B138" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C138" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="D138" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
     </row>
     <row r="139" ht="25.5" customHeight="1" spans="1:4">
@@ -3485,13 +3554,13 @@
         <v>4</v>
       </c>
       <c r="B139" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C139" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="D139" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
     </row>
     <row r="140" ht="25.5" customHeight="1" spans="1:4">
@@ -3499,13 +3568,13 @@
         <v>4</v>
       </c>
       <c r="B140" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C140" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="D140" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
     </row>
     <row r="141" ht="25.5" customHeight="1" spans="1:4">
@@ -3513,13 +3582,13 @@
         <v>4</v>
       </c>
       <c r="B141" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C141" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="D141" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
     </row>
     <row r="142" ht="25.5" customHeight="1" spans="1:4">
@@ -3527,13 +3596,13 @@
         <v>4</v>
       </c>
       <c r="B142" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C142" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="D142" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
     </row>
     <row r="143" ht="25.5" customHeight="1" spans="1:4">
@@ -3541,13 +3610,13 @@
         <v>4</v>
       </c>
       <c r="B143" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C143" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="D143" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
     </row>
     <row r="144" ht="25.5" customHeight="1" spans="1:4">
@@ -3555,13 +3624,13 @@
         <v>4</v>
       </c>
       <c r="B144" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C144" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="D144" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
     </row>
     <row r="145" ht="25.5" customHeight="1" spans="1:4">
@@ -3569,13 +3638,13 @@
         <v>4</v>
       </c>
       <c r="B145" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C145" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="D145" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
     </row>
     <row r="146" ht="25.5" customHeight="1" spans="1:4">
@@ -3583,10 +3652,10 @@
         <v>4</v>
       </c>
       <c r="B146" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="D146" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
     </row>
     <row r="147" ht="25.5" customHeight="1" spans="1:4">
@@ -3594,10 +3663,10 @@
         <v>4</v>
       </c>
       <c r="B147" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="D147" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
     </row>
     <row r="148" ht="25.5" customHeight="1" spans="1:4">
@@ -3605,10 +3674,10 @@
         <v>4</v>
       </c>
       <c r="B148" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="D148" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
     </row>
     <row r="149" ht="25.5" customHeight="1" spans="1:4">
@@ -3616,10 +3685,10 @@
         <v>4</v>
       </c>
       <c r="B149" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="D149" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
     </row>
     <row r="150" ht="25.5" customHeight="1" spans="1:4">
@@ -3627,10 +3696,10 @@
         <v>4</v>
       </c>
       <c r="B150" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="D150" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
     </row>
     <row r="151" ht="25.5" customHeight="1" spans="1:4">
@@ -3638,10 +3707,10 @@
         <v>4</v>
       </c>
       <c r="B151" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="D151" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="152" ht="25.5" customHeight="1" spans="1:4">
@@ -3649,10 +3718,10 @@
         <v>4</v>
       </c>
       <c r="B152" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="D152" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="153" ht="25.5" customHeight="1" spans="1:4">
@@ -3660,10 +3729,10 @@
         <v>4</v>
       </c>
       <c r="B153" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="D153" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
     </row>
     <row r="154" ht="25.5" customHeight="1" spans="1:4">
@@ -3671,10 +3740,10 @@
         <v>4</v>
       </c>
       <c r="B154" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="D154" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
     </row>
     <row r="155" ht="25.5" customHeight="1" spans="1:4">
@@ -3682,27 +3751,107 @@
         <v>4</v>
       </c>
       <c r="B155" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="D155" t="s">
-        <v>179</v>
+        <v>180</v>
+      </c>
+    </row>
+    <row r="156" spans="1:6">
+      <c r="A156" t="s">
+        <v>4</v>
+      </c>
+      <c r="B156" t="s">
+        <v>99</v>
+      </c>
+      <c r="C156" t="s">
+        <v>30</v>
+      </c>
+      <c r="D156" s="5" t="s">
+        <v>181</v>
+      </c>
+      <c r="E156" t="s">
+        <v>182</v>
+      </c>
+      <c r="F156">
+        <v>20260407</v>
+      </c>
+    </row>
+    <row r="157" spans="1:6">
+      <c r="A157" t="s">
+        <v>4</v>
+      </c>
+      <c r="B157" t="s">
+        <v>77</v>
+      </c>
+      <c r="C157" t="s">
+        <v>43</v>
+      </c>
+      <c r="D157" s="5" t="s">
+        <v>183</v>
+      </c>
+      <c r="E157" t="s">
+        <v>182</v>
+      </c>
+      <c r="F157">
+        <v>20260407</v>
+      </c>
+    </row>
+    <row r="158" spans="1:6">
+      <c r="A158" t="s">
+        <v>4</v>
+      </c>
+      <c r="B158" t="s">
+        <v>29</v>
+      </c>
+      <c r="C158" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="D158" s="7" t="s">
+        <v>184</v>
+      </c>
+      <c r="E158" t="s">
+        <v>182</v>
+      </c>
+      <c r="F158">
+        <v>20260407</v>
+      </c>
+    </row>
+    <row r="159" spans="1:6">
+      <c r="A159" t="s">
+        <v>4</v>
+      </c>
+      <c r="B159" t="s">
+        <v>29</v>
+      </c>
+      <c r="C159" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="D159" s="7" t="s">
+        <v>185</v>
+      </c>
+      <c r="E159" t="s">
+        <v>182</v>
+      </c>
+      <c r="F159">
+        <v>20260407</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="D1">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:D159" etc:filterBottomFollowUsedRange="0">
+    <extLst/>
+  </autoFilter>
+  <conditionalFormatting sqref="D$1:D$1048576">
     <cfRule type="duplicateValues" dxfId="0" priority="1"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D2:D1048576">
-    <cfRule type="duplicateValues" dxfId="0" priority="2"/>
   </conditionalFormatting>
   <dataValidations count="3">
     <dataValidation type="list" sqref="B2:B19 B121:B154">
       <formula1>"后勤管理中心,三大区域,商业业务,科创发展中心,战略支持中心,后勤集团总裁室"</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="B20:B120 C2:C19 C121:C154">
+    <dataValidation type="list" sqref="B20:B120 B156:B157 C2:C19 C121:C154">
       <formula1>"教育园特色餐饮,念心湖酒店,海亮后勤车队,海亮医院,中心其余业务部门,中心管理部门,西南区域,东部区域,北部区域,战略支持中心,商超业务-便利店,商超业务-商业街,科创发展中心,线下商超-便利店,线上商城业务,后勤集团总裁室,线下商超-商业街,融爱星餐饮"</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="C20:C120">
+    <dataValidation type="list" sqref="C20:C120 C156:C157">
       <formula1>"区域配送业务,区域餐饮业务,区域商超业务,区域物业业务,区域科技业务,区域总经理室,线下便利店,线上商城,中心餐饮业务,中心物业业务,其他,管理部门,线下商业街"</formula1>
     </dataValidation>
   </dataValidations>

--- a/docs/data/教育后勤2025经营数据看版_组织标签映射表-勿动.xlsx
+++ b/docs/data/教育后勤2025经营数据看版_组织标签映射表-勿动.xlsx
@@ -10,7 +10,7 @@
     <sheet name="组织标签映射表-勿动" sheetId="2" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'组织标签映射表-勿动'!$A$1:$D$159</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'组织标签映射表-勿动'!$A$1:$F$159</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="629" uniqueCount="186">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="654" uniqueCount="184">
   <si>
     <t>level_0</t>
   </si>
@@ -452,16 +452,16 @@
     <t>北部区域总经理室</t>
   </si>
   <si>
+    <t>科创发展中心</t>
+  </si>
+  <si>
     <t>商业业务</t>
   </si>
   <si>
-    <t>管理部门</t>
-  </si>
-  <si>
     <t>后勤数智零售部</t>
   </si>
   <si>
-    <t>线下商超-便利店</t>
+    <t>0421修改映射</t>
   </si>
   <si>
     <t>皓峰初中店</t>
@@ -515,9 +515,6 @@
     <t>宁海公学文创店</t>
   </si>
   <si>
-    <t>线下商超-商业街</t>
-  </si>
-  <si>
     <t>海实文创店</t>
   </si>
   <si>
@@ -558,9 +555,6 @@
   </si>
   <si>
     <t>后勤集团总裁室</t>
-  </si>
-  <si>
-    <t>科创发展中心</t>
   </si>
   <si>
     <t>托管学校入模产品服务</t>
@@ -787,7 +781,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="34">
+  <fills count="35">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -797,6 +791,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF00B0F0"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1132,7 +1132,7 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1156,16 +1156,16 @@
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
@@ -1174,89 +1174,89 @@
     <xf numFmtId="0" fontId="20" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="25" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="25" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="25" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="25" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="25" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="25" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
@@ -1267,6 +1267,7 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -3297,354 +3298,429 @@
         <v>139</v>
       </c>
     </row>
-    <row r="121" s="2" customFormat="1" ht="25.5" customHeight="1" spans="1:4">
+    <row r="121" s="2" customFormat="1" ht="25.5" customHeight="1" spans="1:5">
       <c r="A121" t="s">
         <v>4</v>
       </c>
-      <c r="B121" s="2" t="s">
+      <c r="B121" s="6" t="s">
         <v>140</v>
       </c>
-      <c r="C121" s="2" t="s">
+      <c r="C121" s="6" t="s">
         <v>141</v>
       </c>
       <c r="D121" s="2" t="s">
         <v>142</v>
       </c>
-    </row>
-    <row r="122" ht="25.5" customHeight="1" spans="1:4">
+      <c r="E121" s="6" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="122" ht="25.5" customHeight="1" spans="1:5">
       <c r="A122" t="s">
         <v>4</v>
       </c>
-      <c r="B122" t="s">
+      <c r="B122" s="6" t="s">
         <v>140</v>
       </c>
-      <c r="C122" t="s">
-        <v>143</v>
+      <c r="C122" s="6" t="s">
+        <v>141</v>
       </c>
       <c r="D122" t="s">
         <v>144</v>
       </c>
-    </row>
-    <row r="123" ht="25.5" customHeight="1" spans="1:4">
+      <c r="E122" s="6" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="123" ht="25.5" customHeight="1" spans="1:5">
       <c r="A123" t="s">
         <v>4</v>
       </c>
-      <c r="B123" t="s">
+      <c r="B123" s="6" t="s">
         <v>140</v>
       </c>
-      <c r="C123" t="s">
-        <v>143</v>
+      <c r="C123" s="6" t="s">
+        <v>141</v>
       </c>
       <c r="D123" t="s">
         <v>145</v>
       </c>
-    </row>
-    <row r="124" ht="25.5" customHeight="1" spans="1:4">
+      <c r="E123" s="6" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="124" ht="25.5" customHeight="1" spans="1:5">
       <c r="A124" t="s">
         <v>4</v>
       </c>
-      <c r="B124" t="s">
+      <c r="B124" s="6" t="s">
         <v>140</v>
       </c>
-      <c r="C124" t="s">
-        <v>143</v>
+      <c r="C124" s="6" t="s">
+        <v>141</v>
       </c>
       <c r="D124" t="s">
         <v>146</v>
       </c>
-    </row>
-    <row r="125" ht="25.5" customHeight="1" spans="1:4">
+      <c r="E124" s="6" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="125" ht="25.5" customHeight="1" spans="1:5">
       <c r="A125" t="s">
         <v>4</v>
       </c>
-      <c r="B125" t="s">
+      <c r="B125" s="6" t="s">
         <v>140</v>
       </c>
-      <c r="C125" t="s">
-        <v>143</v>
+      <c r="C125" s="6" t="s">
+        <v>141</v>
       </c>
       <c r="D125" t="s">
         <v>147</v>
       </c>
-    </row>
-    <row r="126" ht="25.5" customHeight="1" spans="1:4">
+      <c r="E125" s="6" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="126" ht="25.5" customHeight="1" spans="1:5">
       <c r="A126" t="s">
         <v>4</v>
       </c>
-      <c r="B126" t="s">
+      <c r="B126" s="6" t="s">
         <v>140</v>
       </c>
-      <c r="C126" t="s">
-        <v>143</v>
+      <c r="C126" s="6" t="s">
+        <v>141</v>
       </c>
       <c r="D126" t="s">
         <v>148</v>
       </c>
-    </row>
-    <row r="127" ht="25.5" customHeight="1" spans="1:4">
+      <c r="E126" s="6" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="127" ht="25.5" customHeight="1" spans="1:5">
       <c r="A127" t="s">
         <v>4</v>
       </c>
-      <c r="B127" t="s">
+      <c r="B127" s="6" t="s">
         <v>140</v>
       </c>
-      <c r="C127" t="s">
-        <v>143</v>
+      <c r="C127" s="6" t="s">
+        <v>141</v>
       </c>
       <c r="D127" t="s">
         <v>149</v>
       </c>
-    </row>
-    <row r="128" ht="25.5" customHeight="1" spans="1:4">
+      <c r="E127" s="6" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="128" ht="25.5" customHeight="1" spans="1:5">
       <c r="A128" t="s">
         <v>4</v>
       </c>
-      <c r="B128" t="s">
+      <c r="B128" s="6" t="s">
         <v>140</v>
       </c>
-      <c r="C128" t="s">
-        <v>143</v>
+      <c r="C128" s="6" t="s">
+        <v>141</v>
       </c>
       <c r="D128" t="s">
         <v>150</v>
       </c>
-    </row>
-    <row r="129" ht="25.5" customHeight="1" spans="1:4">
+      <c r="E128" s="6" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="129" ht="25.5" customHeight="1" spans="1:5">
       <c r="A129" t="s">
         <v>4</v>
       </c>
-      <c r="B129" t="s">
+      <c r="B129" s="6" t="s">
         <v>140</v>
       </c>
-      <c r="C129" t="s">
-        <v>143</v>
+      <c r="C129" s="6" t="s">
+        <v>141</v>
       </c>
       <c r="D129" t="s">
         <v>151</v>
       </c>
-    </row>
-    <row r="130" ht="25.5" customHeight="1" spans="1:4">
+      <c r="E129" s="6" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="130" ht="25.5" customHeight="1" spans="1:5">
       <c r="A130" t="s">
         <v>4</v>
       </c>
-      <c r="B130" t="s">
+      <c r="B130" s="6" t="s">
         <v>140</v>
       </c>
-      <c r="C130" t="s">
-        <v>143</v>
+      <c r="C130" s="6" t="s">
+        <v>141</v>
       </c>
       <c r="D130" t="s">
         <v>152</v>
       </c>
-    </row>
-    <row r="131" ht="25.5" customHeight="1" spans="1:4">
+      <c r="E130" s="6" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="131" ht="25.5" customHeight="1" spans="1:5">
       <c r="A131" t="s">
         <v>4</v>
       </c>
-      <c r="B131" t="s">
+      <c r="B131" s="6" t="s">
         <v>140</v>
       </c>
-      <c r="C131" t="s">
-        <v>143</v>
+      <c r="C131" s="6" t="s">
+        <v>141</v>
       </c>
       <c r="D131" t="s">
         <v>153</v>
       </c>
-    </row>
-    <row r="132" ht="25.5" customHeight="1" spans="1:4">
+      <c r="E131" s="6" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="132" ht="25.5" customHeight="1" spans="1:5">
       <c r="A132" t="s">
         <v>4</v>
       </c>
-      <c r="B132" t="s">
+      <c r="B132" s="6" t="s">
         <v>140</v>
       </c>
-      <c r="C132" t="s">
-        <v>143</v>
+      <c r="C132" s="6" t="s">
+        <v>141</v>
       </c>
       <c r="D132" t="s">
         <v>154</v>
       </c>
-    </row>
-    <row r="133" ht="25.5" customHeight="1" spans="1:4">
+      <c r="E132" s="6" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="133" ht="25.5" customHeight="1" spans="1:5">
       <c r="A133" t="s">
         <v>4</v>
       </c>
-      <c r="B133" t="s">
+      <c r="B133" s="6" t="s">
         <v>140</v>
       </c>
-      <c r="C133" t="s">
-        <v>143</v>
+      <c r="C133" s="6" t="s">
+        <v>141</v>
       </c>
       <c r="D133" t="s">
         <v>155</v>
       </c>
-    </row>
-    <row r="134" ht="25.5" customHeight="1" spans="1:4">
+      <c r="E133" s="6" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="134" ht="25.5" customHeight="1" spans="1:5">
       <c r="A134" t="s">
         <v>4</v>
       </c>
-      <c r="B134" t="s">
+      <c r="B134" s="6" t="s">
         <v>140</v>
       </c>
-      <c r="C134" t="s">
-        <v>143</v>
+      <c r="C134" s="6" t="s">
+        <v>141</v>
       </c>
       <c r="D134" t="s">
         <v>156</v>
       </c>
-    </row>
-    <row r="135" ht="25.5" customHeight="1" spans="1:4">
+      <c r="E134" s="6" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="135" ht="25.5" customHeight="1" spans="1:5">
       <c r="A135" t="s">
         <v>4</v>
       </c>
-      <c r="B135" t="s">
+      <c r="B135" s="6" t="s">
         <v>140</v>
       </c>
-      <c r="C135" t="s">
-        <v>143</v>
+      <c r="C135" s="6" t="s">
+        <v>141</v>
       </c>
       <c r="D135" t="s">
         <v>157</v>
       </c>
-    </row>
-    <row r="136" ht="25.5" customHeight="1" spans="1:4">
+      <c r="E135" s="6" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="136" ht="25.5" customHeight="1" spans="1:5">
       <c r="A136" t="s">
         <v>4</v>
       </c>
-      <c r="B136" t="s">
+      <c r="B136" s="6" t="s">
         <v>140</v>
       </c>
-      <c r="C136" t="s">
-        <v>143</v>
+      <c r="C136" s="6" t="s">
+        <v>141</v>
       </c>
       <c r="D136" t="s">
         <v>158</v>
       </c>
-    </row>
-    <row r="137" ht="25.5" customHeight="1" spans="1:4">
+      <c r="E136" s="6" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="137" ht="25.5" customHeight="1" spans="1:5">
       <c r="A137" t="s">
         <v>4</v>
       </c>
-      <c r="B137" t="s">
+      <c r="B137" s="6" t="s">
         <v>140</v>
       </c>
-      <c r="C137" t="s">
-        <v>143</v>
+      <c r="C137" s="6" t="s">
+        <v>141</v>
       </c>
       <c r="D137" t="s">
         <v>159</v>
       </c>
-    </row>
-    <row r="138" ht="25.5" customHeight="1" spans="1:4">
+      <c r="E137" s="6" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="138" ht="25.5" customHeight="1" spans="1:5">
       <c r="A138" t="s">
         <v>4</v>
       </c>
-      <c r="B138" t="s">
+      <c r="B138" s="6" t="s">
         <v>140</v>
       </c>
-      <c r="C138" t="s">
-        <v>143</v>
+      <c r="C138" s="6" t="s">
+        <v>141</v>
       </c>
       <c r="D138" t="s">
         <v>160</v>
       </c>
-    </row>
-    <row r="139" ht="25.5" customHeight="1" spans="1:4">
+      <c r="E138" s="6" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="139" ht="25.5" customHeight="1" spans="1:5">
       <c r="A139" t="s">
         <v>4</v>
       </c>
-      <c r="B139" t="s">
+      <c r="B139" s="6" t="s">
         <v>140</v>
       </c>
-      <c r="C139" t="s">
+      <c r="C139" s="6" t="s">
+        <v>141</v>
+      </c>
+      <c r="D139" t="s">
         <v>161</v>
       </c>
-      <c r="D139" t="s">
+      <c r="E139" s="6" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="140" ht="25.5" customHeight="1" spans="1:5">
+      <c r="A140" t="s">
+        <v>4</v>
+      </c>
+      <c r="B140" s="6" t="s">
+        <v>140</v>
+      </c>
+      <c r="C140" s="6" t="s">
+        <v>141</v>
+      </c>
+      <c r="D140" t="s">
         <v>162</v>
       </c>
-    </row>
-    <row r="140" ht="25.5" customHeight="1" spans="1:4">
-      <c r="A140" t="s">
-        <v>4</v>
-      </c>
-      <c r="B140" t="s">
+      <c r="E140" s="6" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="141" ht="25.5" customHeight="1" spans="1:5">
+      <c r="A141" t="s">
+        <v>4</v>
+      </c>
+      <c r="B141" s="6" t="s">
         <v>140</v>
       </c>
-      <c r="C140" t="s">
-        <v>161</v>
-      </c>
-      <c r="D140" t="s">
+      <c r="C141" s="6" t="s">
+        <v>141</v>
+      </c>
+      <c r="D141" t="s">
         <v>163</v>
       </c>
-    </row>
-    <row r="141" ht="25.5" customHeight="1" spans="1:4">
-      <c r="A141" t="s">
-        <v>4</v>
-      </c>
-      <c r="B141" t="s">
+      <c r="E141" s="6" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="142" ht="25.5" customHeight="1" spans="1:5">
+      <c r="A142" t="s">
+        <v>4</v>
+      </c>
+      <c r="B142" s="6" t="s">
         <v>140</v>
       </c>
-      <c r="C141" t="s">
-        <v>161</v>
-      </c>
-      <c r="D141" t="s">
+      <c r="C142" s="6" t="s">
+        <v>141</v>
+      </c>
+      <c r="D142" t="s">
         <v>164</v>
       </c>
-    </row>
-    <row r="142" ht="25.5" customHeight="1" spans="1:4">
-      <c r="A142" t="s">
-        <v>4</v>
-      </c>
-      <c r="B142" t="s">
+      <c r="E142" s="6" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="143" ht="25.5" customHeight="1" spans="1:5">
+      <c r="A143" t="s">
+        <v>4</v>
+      </c>
+      <c r="B143" s="6" t="s">
         <v>140</v>
       </c>
-      <c r="C142" t="s">
-        <v>161</v>
-      </c>
-      <c r="D142" t="s">
+      <c r="C143" s="6" t="s">
+        <v>141</v>
+      </c>
+      <c r="D143" t="s">
         <v>165</v>
       </c>
-    </row>
-    <row r="143" ht="25.5" customHeight="1" spans="1:4">
-      <c r="A143" t="s">
-        <v>4</v>
-      </c>
-      <c r="B143" t="s">
+      <c r="E143" s="6" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="144" ht="25.5" customHeight="1" spans="1:5">
+      <c r="A144" t="s">
+        <v>4</v>
+      </c>
+      <c r="B144" s="6" t="s">
         <v>140</v>
       </c>
-      <c r="C143" t="s">
-        <v>161</v>
-      </c>
-      <c r="D143" t="s">
+      <c r="C144" s="6" t="s">
+        <v>141</v>
+      </c>
+      <c r="D144" t="s">
         <v>166</v>
       </c>
-    </row>
-    <row r="144" ht="25.5" customHeight="1" spans="1:4">
-      <c r="A144" t="s">
-        <v>4</v>
-      </c>
-      <c r="B144" t="s">
+      <c r="E144" s="6" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="145" ht="25.5" customHeight="1" spans="1:5">
+      <c r="A145" t="s">
+        <v>4</v>
+      </c>
+      <c r="B145" s="6" t="s">
         <v>140</v>
       </c>
-      <c r="C144" t="s">
-        <v>161</v>
-      </c>
-      <c r="D144" t="s">
+      <c r="C145" s="6" t="s">
+        <v>141</v>
+      </c>
+      <c r="D145" t="s">
         <v>167</v>
       </c>
-    </row>
-    <row r="145" ht="25.5" customHeight="1" spans="1:4">
-      <c r="A145" t="s">
-        <v>4</v>
-      </c>
-      <c r="B145" t="s">
-        <v>140</v>
-      </c>
-      <c r="C145" t="s">
-        <v>168</v>
-      </c>
-      <c r="D145" t="s">
-        <v>168</v>
+      <c r="E145" s="6" t="s">
+        <v>143</v>
       </c>
     </row>
     <row r="146" ht="25.5" customHeight="1" spans="1:4">
@@ -3652,10 +3728,10 @@
         <v>4</v>
       </c>
       <c r="B146" t="s">
+        <v>168</v>
+      </c>
+      <c r="D146" t="s">
         <v>169</v>
-      </c>
-      <c r="D146" t="s">
-        <v>170</v>
       </c>
     </row>
     <row r="147" ht="25.5" customHeight="1" spans="1:4">
@@ -3663,10 +3739,10 @@
         <v>4</v>
       </c>
       <c r="B147" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="D147" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="148" ht="25.5" customHeight="1" spans="1:4">
@@ -3674,10 +3750,10 @@
         <v>4</v>
       </c>
       <c r="B148" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="D148" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="149" ht="25.5" customHeight="1" spans="1:4">
@@ -3685,10 +3761,10 @@
         <v>4</v>
       </c>
       <c r="B149" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="D149" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="150" ht="25.5" customHeight="1" spans="1:4">
@@ -3696,10 +3772,10 @@
         <v>4</v>
       </c>
       <c r="B150" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="D150" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="151" ht="25.5" customHeight="1" spans="1:4">
@@ -3707,10 +3783,10 @@
         <v>4</v>
       </c>
       <c r="B151" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="D151" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="152" ht="25.5" customHeight="1" spans="1:4">
@@ -3718,10 +3794,10 @@
         <v>4</v>
       </c>
       <c r="B152" t="s">
-        <v>176</v>
+        <v>140</v>
       </c>
       <c r="D152" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
     </row>
     <row r="153" ht="25.5" customHeight="1" spans="1:4">
@@ -3729,10 +3805,10 @@
         <v>4</v>
       </c>
       <c r="B153" t="s">
+        <v>140</v>
+      </c>
+      <c r="D153" t="s">
         <v>176</v>
-      </c>
-      <c r="D153" t="s">
-        <v>178</v>
       </c>
     </row>
     <row r="154" ht="25.5" customHeight="1" spans="1:4">
@@ -3740,10 +3816,10 @@
         <v>4</v>
       </c>
       <c r="B154" t="s">
-        <v>176</v>
+        <v>140</v>
       </c>
       <c r="D154" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
     </row>
     <row r="155" ht="25.5" customHeight="1" spans="1:4">
@@ -3751,10 +3827,10 @@
         <v>4</v>
       </c>
       <c r="B155" t="s">
-        <v>176</v>
+        <v>140</v>
       </c>
       <c r="D155" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
     </row>
     <row r="156" spans="1:6">
@@ -3768,10 +3844,10 @@
         <v>30</v>
       </c>
       <c r="D156" s="5" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="E156" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="F156">
         <v>20260407</v>
@@ -3788,10 +3864,10 @@
         <v>43</v>
       </c>
       <c r="D157" s="5" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="E157" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="F157">
         <v>20260407</v>
@@ -3804,14 +3880,14 @@
       <c r="B158" t="s">
         <v>29</v>
       </c>
-      <c r="C158" s="6" t="s">
+      <c r="C158" s="7" t="s">
         <v>36</v>
       </c>
-      <c r="D158" s="7" t="s">
-        <v>184</v>
+      <c r="D158" s="8" t="s">
+        <v>182</v>
       </c>
       <c r="E158" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="F158">
         <v>20260407</v>
@@ -3824,31 +3900,31 @@
       <c r="B159" t="s">
         <v>29</v>
       </c>
-      <c r="C159" s="6" t="s">
+      <c r="C159" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="D159" s="7" t="s">
-        <v>185</v>
+      <c r="D159" s="8" t="s">
+        <v>183</v>
       </c>
       <c r="E159" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="F159">
         <v>20260407</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:D159" etc:filterBottomFollowUsedRange="0">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:F159" etc:filterBottomFollowUsedRange="0">
     <extLst/>
   </autoFilter>
   <conditionalFormatting sqref="D$1:D$1048576">
     <cfRule type="duplicateValues" dxfId="0" priority="1"/>
   </conditionalFormatting>
   <dataValidations count="3">
-    <dataValidation type="list" sqref="B2:B19 B121:B154">
+    <dataValidation type="list" sqref="B2:B19 B121:B154 C121:C145">
       <formula1>"后勤管理中心,三大区域,商业业务,科创发展中心,战略支持中心,后勤集团总裁室"</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="B20:B120 B156:B157 C2:C19 C121:C154">
+    <dataValidation type="list" sqref="B20:B120 B156:B157 C2:C19 C146:C154">
       <formula1>"教育园特色餐饮,念心湖酒店,海亮后勤车队,海亮医院,中心其余业务部门,中心管理部门,西南区域,东部区域,北部区域,战略支持中心,商超业务-便利店,商超业务-商业街,科创发展中心,线下商超-便利店,线上商城业务,后勤集团总裁室,线下商超-商业街,融爱星餐饮"</formula1>
     </dataValidation>
     <dataValidation type="list" sqref="C20:C120 C156:C157">
